--- a/output/version3/test/25-15/MARL/CTDE/RL-RL with CL (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/25-15/MARL/CTDE/RL-RL with CL (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1569</v>
+        <v>1272</v>
       </c>
       <c r="C2" t="n">
-        <v>1238</v>
+        <v>1185</v>
       </c>
       <c r="D2" t="n">
-        <v>1291</v>
+        <v>1140</v>
       </c>
       <c r="E2" t="n">
-        <v>1581</v>
+        <v>1187</v>
       </c>
       <c r="F2" t="n">
-        <v>1301</v>
+        <v>1198</v>
       </c>
       <c r="G2" t="n">
-        <v>1295</v>
+        <v>1161</v>
       </c>
       <c r="H2" t="n">
-        <v>1207</v>
+        <v>1275</v>
       </c>
       <c r="I2" t="n">
-        <v>1153</v>
+        <v>1038</v>
       </c>
       <c r="J2" t="n">
-        <v>1588</v>
+        <v>1121</v>
       </c>
       <c r="K2" t="n">
-        <v>1251</v>
+        <v>1177</v>
       </c>
       <c r="L2" t="n">
-        <v>1347.4</v>
+        <v>1175.4</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>1551</v>
+        <v>1204</v>
       </c>
       <c r="C3" t="n">
-        <v>1128</v>
+        <v>1063</v>
       </c>
       <c r="D3" t="n">
-        <v>1248</v>
+        <v>1218</v>
       </c>
       <c r="E3" t="n">
-        <v>1365</v>
+        <v>1207</v>
       </c>
       <c r="F3" t="n">
-        <v>1142</v>
+        <v>1213</v>
       </c>
       <c r="G3" t="n">
-        <v>1336</v>
+        <v>1381</v>
       </c>
       <c r="H3" t="n">
-        <v>1287</v>
+        <v>1136</v>
       </c>
       <c r="I3" t="n">
-        <v>1188</v>
+        <v>1146</v>
       </c>
       <c r="J3" t="n">
-        <v>1438</v>
+        <v>1086</v>
       </c>
       <c r="K3" t="n">
-        <v>1382</v>
+        <v>1233</v>
       </c>
       <c r="L3" t="n">
-        <v>1306.5</v>
+        <v>1188.7</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>1350</v>
+        <v>1202</v>
       </c>
       <c r="C4" t="n">
-        <v>1088</v>
+        <v>1029</v>
       </c>
       <c r="D4" t="n">
-        <v>1281</v>
+        <v>1184</v>
       </c>
       <c r="E4" t="n">
-        <v>1159</v>
+        <v>1231</v>
       </c>
       <c r="F4" t="n">
-        <v>1247</v>
+        <v>1268</v>
       </c>
       <c r="G4" t="n">
-        <v>1172</v>
+        <v>1313</v>
       </c>
       <c r="H4" t="n">
-        <v>1121</v>
+        <v>1094</v>
       </c>
       <c r="I4" t="n">
-        <v>1281</v>
+        <v>1297</v>
       </c>
       <c r="J4" t="n">
-        <v>1252</v>
+        <v>1148</v>
       </c>
       <c r="K4" t="n">
-        <v>1421</v>
+        <v>1075</v>
       </c>
       <c r="L4" t="n">
-        <v>1237.2</v>
+        <v>1184.1</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>1123</v>
+        <v>998</v>
       </c>
       <c r="C5" t="n">
-        <v>1207</v>
+        <v>1143</v>
       </c>
       <c r="D5" t="n">
-        <v>1227</v>
+        <v>1009</v>
       </c>
       <c r="E5" t="n">
-        <v>1207</v>
+        <v>1038</v>
       </c>
       <c r="F5" t="n">
-        <v>1238</v>
+        <v>1315</v>
       </c>
       <c r="G5" t="n">
-        <v>1234</v>
+        <v>1191</v>
       </c>
       <c r="H5" t="n">
-        <v>1439</v>
+        <v>1087</v>
       </c>
       <c r="I5" t="n">
-        <v>1244</v>
+        <v>1072</v>
       </c>
       <c r="J5" t="n">
-        <v>1122</v>
+        <v>1132</v>
       </c>
       <c r="K5" t="n">
-        <v>1331</v>
+        <v>963</v>
       </c>
       <c r="L5" t="n">
-        <v>1237.2</v>
+        <v>1094.8</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>1354</v>
+        <v>1180</v>
       </c>
       <c r="C6" t="n">
-        <v>1402</v>
+        <v>1151</v>
       </c>
       <c r="D6" t="n">
-        <v>1305</v>
+        <v>1394</v>
       </c>
       <c r="E6" t="n">
-        <v>1562</v>
+        <v>1065</v>
       </c>
       <c r="F6" t="n">
-        <v>1531</v>
+        <v>1409</v>
       </c>
       <c r="G6" t="n">
-        <v>1320</v>
+        <v>1223</v>
       </c>
       <c r="H6" t="n">
-        <v>1269</v>
+        <v>1332</v>
       </c>
       <c r="I6" t="n">
-        <v>1222</v>
+        <v>1159</v>
       </c>
       <c r="J6" t="n">
-        <v>1460</v>
+        <v>1053</v>
       </c>
       <c r="K6" t="n">
-        <v>1351</v>
+        <v>1260</v>
       </c>
       <c r="L6" t="n">
-        <v>1377.6</v>
+        <v>1222.6</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>1054</v>
+        <v>1093</v>
       </c>
       <c r="C7" t="n">
-        <v>950</v>
+        <v>1103</v>
       </c>
       <c r="D7" t="n">
-        <v>1156</v>
+        <v>1047</v>
       </c>
       <c r="E7" t="n">
-        <v>1221</v>
+        <v>1003</v>
       </c>
       <c r="F7" t="n">
-        <v>1250</v>
+        <v>1029</v>
       </c>
       <c r="G7" t="n">
-        <v>1111</v>
+        <v>1180</v>
       </c>
       <c r="H7" t="n">
-        <v>999</v>
+        <v>1138</v>
       </c>
       <c r="I7" t="n">
-        <v>1046</v>
+        <v>1251</v>
       </c>
       <c r="J7" t="n">
-        <v>1301</v>
+        <v>1204</v>
       </c>
       <c r="K7" t="n">
-        <v>1102</v>
+        <v>1068</v>
       </c>
       <c r="L7" t="n">
-        <v>1119</v>
+        <v>1111.6</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>1071</v>
+        <v>1383</v>
       </c>
       <c r="C8" t="n">
-        <v>1196</v>
+        <v>1382</v>
       </c>
       <c r="D8" t="n">
-        <v>1279</v>
+        <v>1103</v>
       </c>
       <c r="E8" t="n">
-        <v>1081</v>
+        <v>1171</v>
       </c>
       <c r="F8" t="n">
-        <v>1183</v>
+        <v>1042</v>
       </c>
       <c r="G8" t="n">
-        <v>1180</v>
+        <v>1195</v>
       </c>
       <c r="H8" t="n">
-        <v>1090</v>
+        <v>1305</v>
       </c>
       <c r="I8" t="n">
-        <v>1282</v>
+        <v>1067</v>
       </c>
       <c r="J8" t="n">
-        <v>1067</v>
+        <v>1057</v>
       </c>
       <c r="K8" t="n">
-        <v>1298</v>
+        <v>1267</v>
       </c>
       <c r="L8" t="n">
-        <v>1172.7</v>
+        <v>1197.2</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>1297</v>
+        <v>989</v>
       </c>
       <c r="C9" t="n">
-        <v>1023</v>
+        <v>961</v>
       </c>
       <c r="D9" t="n">
-        <v>1334</v>
+        <v>1007</v>
       </c>
       <c r="E9" t="n">
-        <v>1172</v>
+        <v>995</v>
       </c>
       <c r="F9" t="n">
-        <v>1132</v>
+        <v>1141</v>
       </c>
       <c r="G9" t="n">
-        <v>1080</v>
+        <v>1050</v>
       </c>
       <c r="H9" t="n">
-        <v>1115</v>
+        <v>1084</v>
       </c>
       <c r="I9" t="n">
-        <v>1284</v>
+        <v>1062</v>
       </c>
       <c r="J9" t="n">
-        <v>1319</v>
+        <v>1017</v>
       </c>
       <c r="K9" t="n">
-        <v>1149</v>
+        <v>1079</v>
       </c>
       <c r="L9" t="n">
-        <v>1190.5</v>
+        <v>1038.5</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>1313</v>
+        <v>1066</v>
       </c>
       <c r="C10" t="n">
-        <v>1097</v>
+        <v>1399</v>
       </c>
       <c r="D10" t="n">
-        <v>1175</v>
+        <v>1081</v>
       </c>
       <c r="E10" t="n">
-        <v>1527</v>
+        <v>1285</v>
       </c>
       <c r="F10" t="n">
-        <v>1300</v>
+        <v>1021</v>
       </c>
       <c r="G10" t="n">
-        <v>1243</v>
+        <v>1122</v>
       </c>
       <c r="H10" t="n">
-        <v>1283</v>
+        <v>1114</v>
       </c>
       <c r="I10" t="n">
-        <v>1454</v>
+        <v>989</v>
       </c>
       <c r="J10" t="n">
-        <v>1099</v>
+        <v>1357</v>
       </c>
       <c r="K10" t="n">
-        <v>1201</v>
+        <v>1140</v>
       </c>
       <c r="L10" t="n">
-        <v>1269.2</v>
+        <v>1157.4</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>1555</v>
+        <v>1220</v>
       </c>
       <c r="C11" t="n">
-        <v>1248</v>
+        <v>1280</v>
       </c>
       <c r="D11" t="n">
-        <v>1336</v>
+        <v>1108</v>
       </c>
       <c r="E11" t="n">
-        <v>1189</v>
+        <v>1096</v>
       </c>
       <c r="F11" t="n">
-        <v>1156</v>
+        <v>1311</v>
       </c>
       <c r="G11" t="n">
-        <v>1517</v>
+        <v>1107</v>
       </c>
       <c r="H11" t="n">
-        <v>1406</v>
+        <v>1100</v>
       </c>
       <c r="I11" t="n">
-        <v>1284</v>
+        <v>1172</v>
       </c>
       <c r="J11" t="n">
-        <v>1311</v>
+        <v>1090</v>
       </c>
       <c r="K11" t="n">
-        <v>1291</v>
+        <v>1097</v>
       </c>
       <c r="L11" t="n">
-        <v>1329.3</v>
+        <v>1158.1</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>1477</v>
+        <v>1104</v>
       </c>
       <c r="C12" t="n">
-        <v>1337</v>
+        <v>1104</v>
       </c>
       <c r="D12" t="n">
-        <v>1493</v>
+        <v>1285</v>
       </c>
       <c r="E12" t="n">
-        <v>1504</v>
+        <v>1043</v>
       </c>
       <c r="F12" t="n">
-        <v>1511</v>
+        <v>1237</v>
       </c>
       <c r="G12" t="n">
+        <v>1274</v>
+      </c>
+      <c r="H12" t="n">
         <v>1290</v>
       </c>
-      <c r="H12" t="n">
-        <v>1377</v>
-      </c>
       <c r="I12" t="n">
-        <v>1207</v>
+        <v>1057</v>
       </c>
       <c r="J12" t="n">
-        <v>1115</v>
+        <v>1280</v>
       </c>
       <c r="K12" t="n">
-        <v>1574</v>
+        <v>1089</v>
       </c>
       <c r="L12" t="n">
-        <v>1388.5</v>
+        <v>1176.3</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>1359</v>
+        <v>1344</v>
       </c>
       <c r="C13" t="n">
-        <v>1473</v>
+        <v>1418</v>
       </c>
       <c r="D13" t="n">
-        <v>1324</v>
+        <v>1351</v>
       </c>
       <c r="E13" t="n">
-        <v>1399</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="n">
-        <v>1432</v>
+        <v>1229</v>
       </c>
       <c r="G13" t="n">
-        <v>1469</v>
+        <v>1297</v>
       </c>
       <c r="H13" t="n">
-        <v>1112</v>
+        <v>1178</v>
       </c>
       <c r="I13" t="n">
-        <v>1322</v>
+        <v>1311</v>
       </c>
       <c r="J13" t="n">
-        <v>1371</v>
+        <v>1311</v>
       </c>
       <c r="K13" t="n">
-        <v>1537</v>
+        <v>1274</v>
       </c>
       <c r="L13" t="n">
-        <v>1379.8</v>
+        <v>1291.7</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>1389</v>
+        <v>1028</v>
       </c>
       <c r="C14" t="n">
-        <v>1174</v>
+        <v>1263</v>
       </c>
       <c r="D14" t="n">
-        <v>1412</v>
+        <v>1064</v>
       </c>
       <c r="E14" t="n">
-        <v>1428</v>
+        <v>1284</v>
       </c>
       <c r="F14" t="n">
-        <v>1174</v>
+        <v>1120</v>
       </c>
       <c r="G14" t="n">
-        <v>1269</v>
+        <v>961</v>
       </c>
       <c r="H14" t="n">
-        <v>1340</v>
+        <v>1165</v>
       </c>
       <c r="I14" t="n">
-        <v>1089</v>
+        <v>1123</v>
       </c>
       <c r="J14" t="n">
-        <v>1132</v>
+        <v>1112</v>
       </c>
       <c r="K14" t="n">
-        <v>1253</v>
+        <v>1242</v>
       </c>
       <c r="L14" t="n">
-        <v>1266</v>
+        <v>1136.2</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>1430</v>
+        <v>1325</v>
       </c>
       <c r="C15" t="n">
-        <v>1202</v>
+        <v>1218</v>
       </c>
       <c r="D15" t="n">
-        <v>1430</v>
+        <v>1156</v>
       </c>
       <c r="E15" t="n">
-        <v>1073</v>
+        <v>1235</v>
       </c>
       <c r="F15" t="n">
-        <v>1226</v>
+        <v>1182</v>
       </c>
       <c r="G15" t="n">
-        <v>1376</v>
+        <v>1197</v>
       </c>
       <c r="H15" t="n">
-        <v>1426</v>
+        <v>1053</v>
       </c>
       <c r="I15" t="n">
-        <v>1133</v>
+        <v>1149</v>
       </c>
       <c r="J15" t="n">
-        <v>1248</v>
+        <v>1134</v>
       </c>
       <c r="K15" t="n">
-        <v>1316</v>
+        <v>1119</v>
       </c>
       <c r="L15" t="n">
-        <v>1286</v>
+        <v>1176.8</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>1023</v>
+        <v>1100</v>
       </c>
       <c r="C16" t="n">
-        <v>1430</v>
+        <v>1161</v>
       </c>
       <c r="D16" t="n">
-        <v>1255</v>
+        <v>1083</v>
       </c>
       <c r="E16" t="n">
-        <v>1228</v>
+        <v>1099</v>
       </c>
       <c r="F16" t="n">
-        <v>1319</v>
+        <v>1171</v>
       </c>
       <c r="G16" t="n">
-        <v>1305</v>
+        <v>1147</v>
       </c>
       <c r="H16" t="n">
-        <v>1123</v>
+        <v>1108</v>
       </c>
       <c r="I16" t="n">
-        <v>1211</v>
+        <v>1388</v>
       </c>
       <c r="J16" t="n">
-        <v>1108</v>
+        <v>1099</v>
       </c>
       <c r="K16" t="n">
-        <v>1128</v>
+        <v>1092</v>
       </c>
       <c r="L16" t="n">
-        <v>1213</v>
+        <v>1144.8</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>1403</v>
+        <v>986</v>
       </c>
       <c r="C17" t="n">
-        <v>1171</v>
+        <v>1250</v>
       </c>
       <c r="D17" t="n">
-        <v>1335</v>
+        <v>1070</v>
       </c>
       <c r="E17" t="n">
-        <v>1450</v>
+        <v>1355</v>
       </c>
       <c r="F17" t="n">
-        <v>1203</v>
+        <v>1228</v>
       </c>
       <c r="G17" t="n">
-        <v>1265</v>
+        <v>1288</v>
       </c>
       <c r="H17" t="n">
-        <v>1320</v>
+        <v>1233</v>
       </c>
       <c r="I17" t="n">
-        <v>1116</v>
+        <v>1209</v>
       </c>
       <c r="J17" t="n">
-        <v>1458</v>
+        <v>1090</v>
       </c>
       <c r="K17" t="n">
-        <v>1306</v>
+        <v>1056</v>
       </c>
       <c r="L17" t="n">
-        <v>1302.7</v>
+        <v>1176.5</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>1222</v>
+        <v>1178</v>
       </c>
       <c r="C18" t="n">
-        <v>1451</v>
+        <v>1212</v>
       </c>
       <c r="D18" t="n">
-        <v>1289</v>
+        <v>1101</v>
       </c>
       <c r="E18" t="n">
-        <v>1083</v>
+        <v>1277</v>
       </c>
       <c r="F18" t="n">
-        <v>1355</v>
+        <v>1126</v>
       </c>
       <c r="G18" t="n">
-        <v>1111</v>
+        <v>1307</v>
       </c>
       <c r="H18" t="n">
-        <v>1297</v>
+        <v>1073</v>
       </c>
       <c r="I18" t="n">
-        <v>1644</v>
+        <v>1147</v>
       </c>
       <c r="J18" t="n">
-        <v>1278</v>
+        <v>992</v>
       </c>
       <c r="K18" t="n">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="L18" t="n">
-        <v>1296.1</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>1236</v>
+        <v>1265</v>
       </c>
       <c r="C19" t="n">
-        <v>1156</v>
+        <v>1063</v>
       </c>
       <c r="D19" t="n">
-        <v>1467</v>
+        <v>1131</v>
       </c>
       <c r="E19" t="n">
-        <v>1421</v>
+        <v>1191</v>
       </c>
       <c r="F19" t="n">
-        <v>1445</v>
+        <v>1226</v>
       </c>
       <c r="G19" t="n">
-        <v>1312</v>
+        <v>1105</v>
       </c>
       <c r="H19" t="n">
-        <v>1530</v>
+        <v>1276</v>
       </c>
       <c r="I19" t="n">
-        <v>1166</v>
+        <v>1255</v>
       </c>
       <c r="J19" t="n">
-        <v>1244</v>
+        <v>1207</v>
       </c>
       <c r="K19" t="n">
         <v>1133</v>
       </c>
       <c r="L19" t="n">
-        <v>1311</v>
+        <v>1185.2</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>1300</v>
+        <v>1211</v>
       </c>
       <c r="C20" t="n">
-        <v>1451</v>
+        <v>1112</v>
       </c>
       <c r="D20" t="n">
+        <v>1235</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1197</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1114</v>
+      </c>
+      <c r="G20" t="n">
         <v>1074</v>
       </c>
-      <c r="E20" t="n">
-        <v>1338</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1264</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1134</v>
-      </c>
       <c r="H20" t="n">
-        <v>1476</v>
+        <v>1058</v>
       </c>
       <c r="I20" t="n">
-        <v>1509</v>
+        <v>1144</v>
       </c>
       <c r="J20" t="n">
-        <v>1540</v>
+        <v>1069</v>
       </c>
       <c r="K20" t="n">
-        <v>1189</v>
+        <v>1202</v>
       </c>
       <c r="L20" t="n">
-        <v>1327.5</v>
+        <v>1141.6</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>1270</v>
+        <v>1214</v>
       </c>
       <c r="C21" t="n">
-        <v>1383</v>
+        <v>1196</v>
       </c>
       <c r="D21" t="n">
-        <v>1507</v>
+        <v>1151</v>
       </c>
       <c r="E21" t="n">
-        <v>1520</v>
+        <v>1178</v>
       </c>
       <c r="F21" t="n">
-        <v>1622</v>
+        <v>1320</v>
       </c>
       <c r="G21" t="n">
-        <v>1207</v>
+        <v>1170</v>
       </c>
       <c r="H21" t="n">
-        <v>1200</v>
+        <v>1289</v>
       </c>
       <c r="I21" t="n">
-        <v>1608</v>
+        <v>1146</v>
       </c>
       <c r="J21" t="n">
-        <v>1423</v>
+        <v>1243</v>
       </c>
       <c r="K21" t="n">
-        <v>1480</v>
+        <v>1101</v>
       </c>
       <c r="L21" t="n">
-        <v>1422</v>
+        <v>1200.8</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>1313</v>
+        <v>1112</v>
       </c>
       <c r="C22" t="n">
-        <v>1457</v>
+        <v>1287</v>
       </c>
       <c r="D22" t="n">
-        <v>1385</v>
+        <v>1230</v>
       </c>
       <c r="E22" t="n">
-        <v>1287</v>
+        <v>1294</v>
       </c>
       <c r="F22" t="n">
-        <v>1209</v>
+        <v>1392</v>
       </c>
       <c r="G22" t="n">
-        <v>1324</v>
+        <v>1221</v>
       </c>
       <c r="H22" t="n">
-        <v>1282</v>
+        <v>1275</v>
       </c>
       <c r="I22" t="n">
-        <v>1165</v>
+        <v>1217</v>
       </c>
       <c r="J22" t="n">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="K22" t="n">
-        <v>1498</v>
+        <v>1270</v>
       </c>
       <c r="L22" t="n">
-        <v>1326.5</v>
+        <v>1263.9</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>1117</v>
+        <v>1020</v>
       </c>
       <c r="C23" t="n">
-        <v>1239</v>
+        <v>1039</v>
       </c>
       <c r="D23" t="n">
-        <v>1123</v>
+        <v>1025</v>
       </c>
       <c r="E23" t="n">
-        <v>1475</v>
+        <v>1230</v>
       </c>
       <c r="F23" t="n">
-        <v>1510</v>
+        <v>1315</v>
       </c>
       <c r="G23" t="n">
-        <v>1385</v>
+        <v>1250</v>
       </c>
       <c r="H23" t="n">
-        <v>1515</v>
+        <v>1129</v>
       </c>
       <c r="I23" t="n">
-        <v>1587</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1461</v>
+        <v>1049</v>
       </c>
       <c r="K23" t="n">
-        <v>1404</v>
+        <v>1067</v>
       </c>
       <c r="L23" t="n">
-        <v>1381.6</v>
+        <v>1112.4</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>1521</v>
+        <v>1143</v>
       </c>
       <c r="C24" t="n">
-        <v>1190</v>
+        <v>1175</v>
       </c>
       <c r="D24" t="n">
-        <v>1223</v>
+        <v>1236</v>
       </c>
       <c r="E24" t="n">
-        <v>1281</v>
+        <v>1240</v>
       </c>
       <c r="F24" t="n">
-        <v>1326</v>
+        <v>1230</v>
       </c>
       <c r="G24" t="n">
-        <v>1174</v>
+        <v>981</v>
       </c>
       <c r="H24" t="n">
-        <v>1438</v>
+        <v>1112</v>
       </c>
       <c r="I24" t="n">
-        <v>1194</v>
+        <v>1045</v>
       </c>
       <c r="J24" t="n">
-        <v>1146</v>
+        <v>1421</v>
       </c>
       <c r="K24" t="n">
-        <v>1424</v>
+        <v>1136</v>
       </c>
       <c r="L24" t="n">
-        <v>1291.7</v>
+        <v>1171.9</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>1318</v>
+        <v>1082</v>
       </c>
       <c r="C25" t="n">
-        <v>1149</v>
+        <v>1381</v>
       </c>
       <c r="D25" t="n">
-        <v>1128</v>
+        <v>1180</v>
       </c>
       <c r="E25" t="n">
-        <v>1348</v>
+        <v>1341</v>
       </c>
       <c r="F25" t="n">
-        <v>1212</v>
+        <v>1220</v>
       </c>
       <c r="G25" t="n">
-        <v>1458</v>
+        <v>1251</v>
       </c>
       <c r="H25" t="n">
-        <v>1329</v>
+        <v>1354</v>
       </c>
       <c r="I25" t="n">
-        <v>1162</v>
+        <v>1104</v>
       </c>
       <c r="J25" t="n">
-        <v>1209</v>
+        <v>1249</v>
       </c>
       <c r="K25" t="n">
-        <v>1564</v>
+        <v>1219</v>
       </c>
       <c r="L25" t="n">
-        <v>1287.7</v>
+        <v>1238.1</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>1181</v>
+        <v>1041</v>
       </c>
       <c r="C26" t="n">
-        <v>1147</v>
+        <v>1032</v>
       </c>
       <c r="D26" t="n">
-        <v>1090</v>
+        <v>1101</v>
       </c>
       <c r="E26" t="n">
+        <v>1193</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1072</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1053</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1250</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1053</v>
+      </c>
+      <c r="J26" t="n">
         <v>1120</v>
       </c>
-      <c r="F26" t="n">
-        <v>1136</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1281</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1211</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1224</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1128</v>
-      </c>
       <c r="K26" t="n">
-        <v>1106</v>
+        <v>1308</v>
       </c>
       <c r="L26" t="n">
-        <v>1162.4</v>
+        <v>1122.3</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1639</v>
+        <v>1162</v>
       </c>
       <c r="C27" t="n">
-        <v>1266</v>
+        <v>1128</v>
       </c>
       <c r="D27" t="n">
-        <v>1216</v>
+        <v>1151</v>
       </c>
       <c r="E27" t="n">
-        <v>1337</v>
+        <v>1201</v>
       </c>
       <c r="F27" t="n">
-        <v>1369</v>
+        <v>1268</v>
       </c>
       <c r="G27" t="n">
-        <v>1415</v>
+        <v>1026</v>
       </c>
       <c r="H27" t="n">
-        <v>1282</v>
+        <v>1121</v>
       </c>
       <c r="I27" t="n">
-        <v>1295</v>
+        <v>1235</v>
       </c>
       <c r="J27" t="n">
-        <v>1264</v>
+        <v>1236</v>
       </c>
       <c r="K27" t="n">
-        <v>1338</v>
+        <v>1412</v>
       </c>
       <c r="L27" t="n">
-        <v>1342.1</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>1259</v>
+        <v>1183</v>
       </c>
       <c r="C28" t="n">
-        <v>1360</v>
+        <v>1043</v>
       </c>
       <c r="D28" t="n">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="E28" t="n">
-        <v>1293</v>
+        <v>1173</v>
       </c>
       <c r="F28" t="n">
-        <v>1177</v>
+        <v>1200</v>
       </c>
       <c r="G28" t="n">
-        <v>1483</v>
+        <v>1109</v>
       </c>
       <c r="H28" t="n">
-        <v>1241</v>
+        <v>1086</v>
       </c>
       <c r="I28" t="n">
-        <v>1103</v>
+        <v>1295</v>
       </c>
       <c r="J28" t="n">
-        <v>1151</v>
+        <v>1125</v>
       </c>
       <c r="K28" t="n">
-        <v>1257</v>
+        <v>1093</v>
       </c>
       <c r="L28" t="n">
-        <v>1253.5</v>
+        <v>1152.1</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>1176</v>
+        <v>1095</v>
       </c>
       <c r="C29" t="n">
-        <v>1157</v>
+        <v>1018</v>
       </c>
       <c r="D29" t="n">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="E29" t="n">
-        <v>1206</v>
+        <v>1127</v>
       </c>
       <c r="F29" t="n">
-        <v>1164</v>
+        <v>1074</v>
       </c>
       <c r="G29" t="n">
-        <v>1122</v>
+        <v>981</v>
       </c>
       <c r="H29" t="n">
-        <v>1200</v>
+        <v>1040</v>
       </c>
       <c r="I29" t="n">
-        <v>1277</v>
+        <v>1041</v>
       </c>
       <c r="J29" t="n">
-        <v>1197</v>
+        <v>1003</v>
       </c>
       <c r="K29" t="n">
-        <v>1206</v>
+        <v>1033</v>
       </c>
       <c r="L29" t="n">
-        <v>1178.5</v>
+        <v>1048.7</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>1511</v>
+        <v>1297</v>
       </c>
       <c r="C30" t="n">
-        <v>1077</v>
+        <v>1259</v>
       </c>
       <c r="D30" t="n">
-        <v>1231</v>
+        <v>1160</v>
       </c>
       <c r="E30" t="n">
-        <v>1089</v>
+        <v>948</v>
       </c>
       <c r="F30" t="n">
-        <v>1232</v>
+        <v>1180</v>
       </c>
       <c r="G30" t="n">
-        <v>1164</v>
+        <v>1111</v>
       </c>
       <c r="H30" t="n">
-        <v>1277</v>
+        <v>1189</v>
       </c>
       <c r="I30" t="n">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="J30" t="n">
-        <v>1082</v>
+        <v>1262</v>
       </c>
       <c r="K30" t="n">
-        <v>1272</v>
+        <v>1058</v>
       </c>
       <c r="L30" t="n">
-        <v>1208.1</v>
+        <v>1160.8</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1237</v>
+        <v>1330</v>
       </c>
       <c r="C31" t="n">
-        <v>1275</v>
+        <v>1139</v>
       </c>
       <c r="D31" t="n">
-        <v>1311</v>
+        <v>1286</v>
       </c>
       <c r="E31" t="n">
-        <v>1533</v>
+        <v>1076</v>
       </c>
       <c r="F31" t="n">
-        <v>1267</v>
+        <v>1084</v>
       </c>
       <c r="G31" t="n">
-        <v>1299</v>
+        <v>1116</v>
       </c>
       <c r="H31" t="n">
+        <v>1181</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1133</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1298</v>
+      </c>
+      <c r="K31" t="n">
         <v>1157</v>
       </c>
-      <c r="I31" t="n">
-        <v>1572</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1170</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1251</v>
-      </c>
       <c r="L31" t="n">
-        <v>1307.2</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>1166</v>
+        <v>1206</v>
       </c>
       <c r="C32" t="n">
-        <v>1136</v>
+        <v>1116</v>
       </c>
       <c r="D32" t="n">
-        <v>1336</v>
+        <v>1008</v>
       </c>
       <c r="E32" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1090</v>
+      </c>
+      <c r="G32" t="n">
         <v>1148</v>
       </c>
-      <c r="F32" t="n">
-        <v>1082</v>
-      </c>
-      <c r="G32" t="n">
-        <v>984</v>
-      </c>
       <c r="H32" t="n">
-        <v>1100</v>
+        <v>1074</v>
       </c>
       <c r="I32" t="n">
-        <v>1229</v>
+        <v>1181</v>
       </c>
       <c r="J32" t="n">
-        <v>1083</v>
+        <v>963</v>
       </c>
       <c r="K32" t="n">
-        <v>1242</v>
+        <v>949</v>
       </c>
       <c r="L32" t="n">
-        <v>1150.6</v>
+        <v>1099.5</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>1215</v>
+        <v>1165</v>
       </c>
       <c r="C33" t="n">
-        <v>1254</v>
+        <v>1090</v>
       </c>
       <c r="D33" t="n">
-        <v>1088</v>
+        <v>1349</v>
       </c>
       <c r="E33" t="n">
-        <v>1191</v>
+        <v>1334</v>
       </c>
       <c r="F33" t="n">
-        <v>1370</v>
+        <v>1009</v>
       </c>
       <c r="G33" t="n">
-        <v>1137</v>
+        <v>1128</v>
       </c>
       <c r="H33" t="n">
-        <v>1154</v>
+        <v>1251</v>
       </c>
       <c r="I33" t="n">
-        <v>1254</v>
+        <v>1095</v>
       </c>
       <c r="J33" t="n">
-        <v>1211</v>
+        <v>1150</v>
       </c>
       <c r="K33" t="n">
-        <v>1417</v>
+        <v>1159</v>
       </c>
       <c r="L33" t="n">
-        <v>1229.1</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>1222</v>
+        <v>1235</v>
       </c>
       <c r="C34" t="n">
-        <v>1132</v>
+        <v>1101</v>
       </c>
       <c r="D34" t="n">
-        <v>1172</v>
+        <v>1218</v>
       </c>
       <c r="E34" t="n">
-        <v>1222</v>
+        <v>1232</v>
       </c>
       <c r="F34" t="n">
-        <v>1442</v>
+        <v>1079</v>
       </c>
       <c r="G34" t="n">
-        <v>1224</v>
+        <v>1038</v>
       </c>
       <c r="H34" t="n">
-        <v>1243</v>
+        <v>1367</v>
       </c>
       <c r="I34" t="n">
-        <v>1093</v>
+        <v>1062</v>
       </c>
       <c r="J34" t="n">
-        <v>1335</v>
+        <v>1098</v>
       </c>
       <c r="K34" t="n">
-        <v>1282</v>
+        <v>1008</v>
       </c>
       <c r="L34" t="n">
-        <v>1236.7</v>
+        <v>1143.8</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>1328</v>
+        <v>1078</v>
       </c>
       <c r="C35" t="n">
-        <v>1090</v>
+        <v>1069</v>
       </c>
       <c r="D35" t="n">
-        <v>1083</v>
+        <v>1141</v>
       </c>
       <c r="E35" t="n">
-        <v>1369</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="n">
-        <v>1347</v>
+        <v>1376</v>
       </c>
       <c r="G35" t="n">
-        <v>1505</v>
+        <v>1175</v>
       </c>
       <c r="H35" t="n">
-        <v>1421</v>
+        <v>1005</v>
       </c>
       <c r="I35" t="n">
-        <v>1393</v>
+        <v>1009</v>
       </c>
       <c r="J35" t="n">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="K35" t="n">
-        <v>1092</v>
+        <v>1201</v>
       </c>
       <c r="L35" t="n">
-        <v>1285.7</v>
+        <v>1149.5</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1117</v>
+        <v>1088</v>
       </c>
       <c r="C36" t="n">
-        <v>1019</v>
+        <v>1035</v>
       </c>
       <c r="D36" t="n">
-        <v>1128</v>
+        <v>1142</v>
       </c>
       <c r="E36" t="n">
-        <v>1211</v>
+        <v>988</v>
       </c>
       <c r="F36" t="n">
-        <v>1341</v>
+        <v>1275</v>
       </c>
       <c r="G36" t="n">
-        <v>1158</v>
+        <v>1096</v>
       </c>
       <c r="H36" t="n">
-        <v>1136</v>
+        <v>1036</v>
       </c>
       <c r="I36" t="n">
-        <v>1127</v>
+        <v>1081</v>
       </c>
       <c r="J36" t="n">
-        <v>1197</v>
+        <v>1246</v>
       </c>
       <c r="K36" t="n">
-        <v>1131</v>
+        <v>1180</v>
       </c>
       <c r="L36" t="n">
-        <v>1156.5</v>
+        <v>1116.7</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>1139</v>
+        <v>997</v>
       </c>
       <c r="C37" t="n">
-        <v>1267</v>
+        <v>1093</v>
       </c>
       <c r="D37" t="n">
-        <v>1306</v>
+        <v>1076</v>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>1295</v>
       </c>
       <c r="F37" t="n">
-        <v>1245</v>
+        <v>1317</v>
       </c>
       <c r="G37" t="n">
-        <v>1172</v>
+        <v>1181</v>
       </c>
       <c r="H37" t="n">
-        <v>1174</v>
+        <v>1102</v>
       </c>
       <c r="I37" t="n">
-        <v>1154</v>
+        <v>1059</v>
       </c>
       <c r="J37" t="n">
-        <v>1266</v>
+        <v>978</v>
       </c>
       <c r="K37" t="n">
-        <v>1151</v>
+        <v>1107</v>
       </c>
       <c r="L37" t="n">
-        <v>1198.2</v>
+        <v>1120.5</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>1322</v>
+        <v>1150</v>
       </c>
       <c r="C38" t="n">
-        <v>1347</v>
+        <v>1182</v>
       </c>
       <c r="D38" t="n">
-        <v>1153</v>
+        <v>1066</v>
       </c>
       <c r="E38" t="n">
-        <v>1166</v>
+        <v>1044</v>
       </c>
       <c r="F38" t="n">
-        <v>1376</v>
+        <v>1034</v>
       </c>
       <c r="G38" t="n">
-        <v>1166</v>
+        <v>1052</v>
       </c>
       <c r="H38" t="n">
-        <v>1094</v>
+        <v>1175</v>
       </c>
       <c r="I38" t="n">
-        <v>1176</v>
+        <v>1201</v>
       </c>
       <c r="J38" t="n">
-        <v>1152</v>
+        <v>1086</v>
       </c>
       <c r="K38" t="n">
-        <v>1178</v>
+        <v>1261</v>
       </c>
       <c r="L38" t="n">
-        <v>1213</v>
+        <v>1125.1</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>1397</v>
+        <v>1104</v>
       </c>
       <c r="C39" t="n">
-        <v>1226</v>
+        <v>1075</v>
       </c>
       <c r="D39" t="n">
-        <v>1166</v>
+        <v>1000</v>
       </c>
       <c r="E39" t="n">
-        <v>1320</v>
+        <v>956</v>
       </c>
       <c r="F39" t="n">
-        <v>1286</v>
+        <v>1063</v>
       </c>
       <c r="G39" t="n">
         <v>1132</v>
       </c>
       <c r="H39" t="n">
-        <v>1108</v>
+        <v>1124</v>
       </c>
       <c r="I39" t="n">
-        <v>1103</v>
+        <v>1215</v>
       </c>
       <c r="J39" t="n">
-        <v>1276</v>
+        <v>1101</v>
       </c>
       <c r="K39" t="n">
-        <v>1183</v>
+        <v>1075</v>
       </c>
       <c r="L39" t="n">
-        <v>1219.7</v>
+        <v>1084.5</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>1322</v>
+        <v>1029</v>
       </c>
       <c r="C40" t="n">
-        <v>1150</v>
+        <v>1209</v>
       </c>
       <c r="D40" t="n">
-        <v>1339</v>
+        <v>1318</v>
       </c>
       <c r="E40" t="n">
-        <v>1546</v>
+        <v>1218</v>
       </c>
       <c r="F40" t="n">
-        <v>1517</v>
+        <v>1110</v>
       </c>
       <c r="G40" t="n">
-        <v>1407</v>
+        <v>1185</v>
       </c>
       <c r="H40" t="n">
-        <v>1379</v>
+        <v>1160</v>
       </c>
       <c r="I40" t="n">
-        <v>1179</v>
+        <v>1255</v>
       </c>
       <c r="J40" t="n">
-        <v>1107</v>
+        <v>1212</v>
       </c>
       <c r="K40" t="n">
-        <v>1215</v>
+        <v>1279</v>
       </c>
       <c r="L40" t="n">
-        <v>1316.1</v>
+        <v>1197.5</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>1411</v>
+        <v>1219</v>
       </c>
       <c r="C41" t="n">
-        <v>1471</v>
+        <v>1108</v>
       </c>
       <c r="D41" t="n">
-        <v>1363</v>
+        <v>1059</v>
       </c>
       <c r="E41" t="n">
-        <v>1193</v>
+        <v>1067</v>
       </c>
       <c r="F41" t="n">
-        <v>1041</v>
+        <v>1129</v>
       </c>
       <c r="G41" t="n">
-        <v>1417</v>
+        <v>1130</v>
       </c>
       <c r="H41" t="n">
-        <v>1157</v>
+        <v>1172</v>
       </c>
       <c r="I41" t="n">
-        <v>1187</v>
+        <v>1298</v>
       </c>
       <c r="J41" t="n">
-        <v>1488</v>
+        <v>1309</v>
       </c>
       <c r="K41" t="n">
-        <v>1346</v>
+        <v>1089</v>
       </c>
       <c r="L41" t="n">
-        <v>1307.4</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>1119</v>
+        <v>1202</v>
       </c>
       <c r="C42" t="n">
-        <v>1087</v>
+        <v>1200</v>
       </c>
       <c r="D42" t="n">
-        <v>1178</v>
+        <v>1013</v>
       </c>
       <c r="E42" t="n">
-        <v>1024</v>
+        <v>1198</v>
       </c>
       <c r="F42" t="n">
-        <v>1303</v>
+        <v>1148</v>
       </c>
       <c r="G42" t="n">
-        <v>1022</v>
+        <v>1136</v>
       </c>
       <c r="H42" t="n">
-        <v>1206</v>
+        <v>1051</v>
       </c>
       <c r="I42" t="n">
-        <v>1383</v>
+        <v>1338</v>
       </c>
       <c r="J42" t="n">
-        <v>1247</v>
+        <v>1073</v>
       </c>
       <c r="K42" t="n">
-        <v>1293</v>
+        <v>1063</v>
       </c>
       <c r="L42" t="n">
-        <v>1186.2</v>
+        <v>1142.2</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>1393</v>
+        <v>1096</v>
       </c>
       <c r="C43" t="n">
-        <v>1185</v>
+        <v>1160</v>
       </c>
       <c r="D43" t="n">
-        <v>1226</v>
+        <v>1187</v>
       </c>
       <c r="E43" t="n">
-        <v>1343</v>
+        <v>1195</v>
       </c>
       <c r="F43" t="n">
-        <v>1405</v>
+        <v>1177</v>
       </c>
       <c r="G43" t="n">
-        <v>1238</v>
+        <v>1104</v>
       </c>
       <c r="H43" t="n">
-        <v>1376</v>
+        <v>1213</v>
       </c>
       <c r="I43" t="n">
-        <v>1258</v>
+        <v>1177</v>
       </c>
       <c r="J43" t="n">
-        <v>1437</v>
+        <v>1199</v>
       </c>
       <c r="K43" t="n">
-        <v>1519</v>
+        <v>1138</v>
       </c>
       <c r="L43" t="n">
-        <v>1338</v>
+        <v>1164.6</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>1333</v>
+        <v>1091</v>
       </c>
       <c r="C44" t="n">
-        <v>1264</v>
+        <v>1138</v>
       </c>
       <c r="D44" t="n">
-        <v>1206</v>
+        <v>1213</v>
       </c>
       <c r="E44" t="n">
-        <v>1067</v>
+        <v>1171</v>
       </c>
       <c r="F44" t="n">
-        <v>1083</v>
+        <v>1137</v>
       </c>
       <c r="G44" t="n">
-        <v>1253</v>
+        <v>1005</v>
       </c>
       <c r="H44" t="n">
-        <v>1432</v>
+        <v>1061</v>
       </c>
       <c r="I44" t="n">
-        <v>1132</v>
+        <v>1127</v>
       </c>
       <c r="J44" t="n">
-        <v>1277</v>
+        <v>1048</v>
       </c>
       <c r="K44" t="n">
-        <v>1210</v>
+        <v>1129</v>
       </c>
       <c r="L44" t="n">
-        <v>1225.7</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>1184</v>
+        <v>988</v>
       </c>
       <c r="C45" t="n">
-        <v>1289</v>
+        <v>1075</v>
       </c>
       <c r="D45" t="n">
-        <v>1296</v>
+        <v>922</v>
       </c>
       <c r="E45" t="n">
-        <v>1561</v>
+        <v>1379</v>
       </c>
       <c r="F45" t="n">
-        <v>1275</v>
+        <v>1083</v>
       </c>
       <c r="G45" t="n">
-        <v>1073</v>
+        <v>1141</v>
       </c>
       <c r="H45" t="n">
-        <v>1222</v>
+        <v>1155</v>
       </c>
       <c r="I45" t="n">
-        <v>1386</v>
+        <v>1159</v>
       </c>
       <c r="J45" t="n">
-        <v>1250</v>
+        <v>1090</v>
       </c>
       <c r="K45" t="n">
-        <v>1150</v>
+        <v>1164</v>
       </c>
       <c r="L45" t="n">
-        <v>1268.6</v>
+        <v>1115.6</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>1185</v>
+        <v>1110</v>
       </c>
       <c r="C46" t="n">
-        <v>1186</v>
+        <v>1076</v>
       </c>
       <c r="D46" t="n">
-        <v>1351</v>
+        <v>1254</v>
       </c>
       <c r="E46" t="n">
-        <v>1266</v>
+        <v>1252</v>
       </c>
       <c r="F46" t="n">
-        <v>1193</v>
+        <v>1204</v>
       </c>
       <c r="G46" t="n">
-        <v>1171</v>
+        <v>1357</v>
       </c>
       <c r="H46" t="n">
-        <v>1582</v>
+        <v>1278</v>
       </c>
       <c r="I46" t="n">
-        <v>1310</v>
+        <v>1346</v>
       </c>
       <c r="J46" t="n">
-        <v>1091</v>
+        <v>1349</v>
       </c>
       <c r="K46" t="n">
-        <v>1265</v>
+        <v>1172</v>
       </c>
       <c r="L46" t="n">
-        <v>1260</v>
+        <v>1239.8</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>1636</v>
+        <v>1440</v>
       </c>
       <c r="C47" t="n">
-        <v>1578</v>
+        <v>1140</v>
       </c>
       <c r="D47" t="n">
-        <v>1735</v>
+        <v>1206</v>
       </c>
       <c r="E47" t="n">
-        <v>1477</v>
+        <v>1279</v>
       </c>
       <c r="F47" t="n">
-        <v>1381</v>
+        <v>1313</v>
       </c>
       <c r="G47" t="n">
-        <v>1516</v>
+        <v>1126</v>
       </c>
       <c r="H47" t="n">
-        <v>1196</v>
+        <v>1164</v>
       </c>
       <c r="I47" t="n">
-        <v>1158</v>
+        <v>1327</v>
       </c>
       <c r="J47" t="n">
-        <v>1131</v>
+        <v>1195</v>
       </c>
       <c r="K47" t="n">
-        <v>1524</v>
+        <v>1192</v>
       </c>
       <c r="L47" t="n">
-        <v>1433.2</v>
+        <v>1238.2</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>1501</v>
+        <v>1121</v>
       </c>
       <c r="C48" t="n">
-        <v>1252</v>
+        <v>1060</v>
       </c>
       <c r="D48" t="n">
-        <v>1221</v>
+        <v>1167</v>
       </c>
       <c r="E48" t="n">
-        <v>1219</v>
+        <v>1127</v>
       </c>
       <c r="F48" t="n">
-        <v>1058</v>
+        <v>1126</v>
       </c>
       <c r="G48" t="n">
-        <v>1374</v>
+        <v>1140</v>
       </c>
       <c r="H48" t="n">
-        <v>1224</v>
+        <v>1131</v>
       </c>
       <c r="I48" t="n">
-        <v>1558</v>
+        <v>1381</v>
       </c>
       <c r="J48" t="n">
-        <v>1320</v>
+        <v>1118</v>
       </c>
       <c r="K48" t="n">
-        <v>1231</v>
+        <v>1178</v>
       </c>
       <c r="L48" t="n">
-        <v>1295.8</v>
+        <v>1154.9</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>1598</v>
+        <v>1133</v>
       </c>
       <c r="C49" t="n">
-        <v>1566</v>
+        <v>1222</v>
       </c>
       <c r="D49" t="n">
-        <v>1407</v>
+        <v>1083</v>
       </c>
       <c r="E49" t="n">
-        <v>1283</v>
+        <v>1230</v>
       </c>
       <c r="F49" t="n">
-        <v>1231</v>
+        <v>1190</v>
       </c>
       <c r="G49" t="n">
-        <v>1312</v>
+        <v>1137</v>
       </c>
       <c r="H49" t="n">
-        <v>1612</v>
+        <v>1213</v>
       </c>
       <c r="I49" t="n">
-        <v>1305</v>
+        <v>1167</v>
       </c>
       <c r="J49" t="n">
-        <v>1224</v>
+        <v>1103</v>
       </c>
       <c r="K49" t="n">
-        <v>1647</v>
+        <v>1113</v>
       </c>
       <c r="L49" t="n">
-        <v>1418.5</v>
+        <v>1159.1</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>1217</v>
+        <v>1304</v>
       </c>
       <c r="C50" t="n">
-        <v>1194</v>
+        <v>1071</v>
       </c>
       <c r="D50" t="n">
-        <v>1055</v>
+        <v>1067</v>
       </c>
       <c r="E50" t="n">
-        <v>1070</v>
+        <v>1244</v>
       </c>
       <c r="F50" t="n">
-        <v>1497</v>
+        <v>1180</v>
       </c>
       <c r="G50" t="n">
-        <v>1020</v>
+        <v>1067</v>
       </c>
       <c r="H50" t="n">
-        <v>1122</v>
+        <v>1115</v>
       </c>
       <c r="I50" t="n">
-        <v>1239</v>
+        <v>1099</v>
       </c>
       <c r="J50" t="n">
-        <v>1089</v>
+        <v>1120</v>
       </c>
       <c r="K50" t="n">
-        <v>1162</v>
+        <v>937</v>
       </c>
       <c r="L50" t="n">
-        <v>1166.5</v>
+        <v>1120.4</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>1185</v>
+        <v>1034</v>
       </c>
       <c r="C51" t="n">
-        <v>1093</v>
+        <v>1075</v>
       </c>
       <c r="D51" t="n">
-        <v>1130</v>
+        <v>1271</v>
       </c>
       <c r="E51" t="n">
-        <v>1047</v>
+        <v>1076</v>
       </c>
       <c r="F51" t="n">
-        <v>1290</v>
+        <v>1120</v>
       </c>
       <c r="G51" t="n">
-        <v>1112</v>
+        <v>1208</v>
       </c>
       <c r="H51" t="n">
-        <v>1133</v>
+        <v>983</v>
       </c>
       <c r="I51" t="n">
-        <v>1190</v>
+        <v>1258</v>
       </c>
       <c r="J51" t="n">
-        <v>1100</v>
+        <v>1085</v>
       </c>
       <c r="K51" t="n">
-        <v>1090</v>
+        <v>1014</v>
       </c>
       <c r="L51" t="n">
-        <v>1137</v>
+        <v>1112.4</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1312.16</v>
+        <v>1152.34</v>
       </c>
       <c r="C52" t="n">
-        <v>1238.16</v>
+        <v>1149.78</v>
       </c>
       <c r="D52" t="n">
-        <v>1263.1</v>
+        <v>1146.72</v>
       </c>
       <c r="E52" t="n">
-        <v>1286.16</v>
+        <v>1178.36</v>
       </c>
       <c r="F52" t="n">
-        <v>1287.92</v>
+        <v>1181.9</v>
       </c>
       <c r="G52" t="n">
-        <v>1254.48</v>
+        <v>1150.56</v>
       </c>
       <c r="H52" t="n">
-        <v>1268.4</v>
+        <v>1159.1</v>
       </c>
       <c r="I52" t="n">
-        <v>1259.64</v>
+        <v>1165.68</v>
       </c>
       <c r="J52" t="n">
-        <v>1250.74</v>
+        <v>1153.22</v>
       </c>
       <c r="K52" t="n">
-        <v>1291.44</v>
+        <v>1141.1</v>
       </c>
       <c r="L52" t="n">
-        <v>1271.22</v>
+        <v>1157.876</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>20.22102952003479</v>
+        <v>15.77481532096863</v>
       </c>
       <c r="C2" t="n">
-        <v>13.97241401672363</v>
+        <v>12.96245741844177</v>
       </c>
       <c r="D2" t="n">
-        <v>12.17250037193298</v>
+        <v>11.92610788345337</v>
       </c>
       <c r="E2" t="n">
-        <v>16.84609031677246</v>
+        <v>12.93939661979675</v>
       </c>
       <c r="F2" t="n">
-        <v>12.72507953643799</v>
+        <v>14.26784443855286</v>
       </c>
       <c r="G2" t="n">
-        <v>14.71108198165894</v>
+        <v>12.9443838596344</v>
       </c>
       <c r="H2" t="n">
-        <v>13.16980218887329</v>
+        <v>16.7133047580719</v>
       </c>
       <c r="I2" t="n">
-        <v>11.84119343757629</v>
+        <v>11.54412913322449</v>
       </c>
       <c r="J2" t="n">
-        <v>20.38110709190369</v>
+        <v>13.30641603469849</v>
       </c>
       <c r="K2" t="n">
-        <v>13.58918356895447</v>
+        <v>13.72230315208435</v>
       </c>
       <c r="L2" t="n">
-        <v>14.96294820308685</v>
+        <v>13.6101158618927</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>16.5443959236145</v>
+        <v>14.11724662780762</v>
       </c>
       <c r="C3" t="n">
-        <v>11.22280120849609</v>
+        <v>11.40549945831299</v>
       </c>
       <c r="D3" t="n">
-        <v>13.08794021606445</v>
+        <v>11.11028981208801</v>
       </c>
       <c r="E3" t="n">
-        <v>16.49707961082458</v>
+        <v>11.3785707950592</v>
       </c>
       <c r="F3" t="n">
-        <v>12.80937910079956</v>
+        <v>12.01686477661133</v>
       </c>
       <c r="G3" t="n">
-        <v>15.6276376247406</v>
+        <v>14.91012787818909</v>
       </c>
       <c r="H3" t="n">
-        <v>12.22832775115967</v>
+        <v>10.93475770950317</v>
       </c>
       <c r="I3" t="n">
-        <v>11.7754979133606</v>
+        <v>12.28614330291748</v>
       </c>
       <c r="J3" t="n">
-        <v>17.28996109962463</v>
+        <v>10.69739317893982</v>
       </c>
       <c r="K3" t="n">
-        <v>15.03866028785706</v>
+        <v>16.38717699050903</v>
       </c>
       <c r="L3" t="n">
-        <v>14.21216807365417</v>
+        <v>12.52440705299377</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>13.94104957580566</v>
+        <v>11.74957942962646</v>
       </c>
       <c r="C4" t="n">
-        <v>14.34696459770203</v>
+        <v>10.98327088356018</v>
       </c>
       <c r="D4" t="n">
-        <v>16.62565493583679</v>
+        <v>15.94136881828308</v>
       </c>
       <c r="E4" t="n">
-        <v>12.54956245422363</v>
+        <v>15.86158323287964</v>
       </c>
       <c r="F4" t="n">
-        <v>14.38981246948242</v>
+        <v>13.07503414154053</v>
       </c>
       <c r="G4" t="n">
-        <v>12.69113945960999</v>
+        <v>16.77115106582642</v>
       </c>
       <c r="H4" t="n">
-        <v>12.98495769500732</v>
+        <v>12.00688648223877</v>
       </c>
       <c r="I4" t="n">
-        <v>13.49160623550415</v>
+        <v>18.22526097297668</v>
       </c>
       <c r="J4" t="n">
-        <v>16.41618037223816</v>
+        <v>12.8895308971405</v>
       </c>
       <c r="K4" t="n">
-        <v>15.45363402366638</v>
+        <v>11.92728042602539</v>
       </c>
       <c r="L4" t="n">
-        <v>14.28905618190765</v>
+        <v>13.94309463500977</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>13.61229491233826</v>
+        <v>10.98263072967529</v>
       </c>
       <c r="C5" t="n">
-        <v>11.37405943870544</v>
+        <v>14.92309284210205</v>
       </c>
       <c r="D5" t="n">
-        <v>14.18693995475769</v>
+        <v>12.53447961807251</v>
       </c>
       <c r="E5" t="n">
-        <v>12.8697144985199</v>
+        <v>10.8140811920166</v>
       </c>
       <c r="F5" t="n">
-        <v>12.28873920440674</v>
+        <v>15.63119840621948</v>
       </c>
       <c r="G5" t="n">
-        <v>11.58151865005493</v>
+        <v>16.43305444717407</v>
       </c>
       <c r="H5" t="n">
-        <v>16.81363463401794</v>
+        <v>11.66380834579468</v>
       </c>
       <c r="I5" t="n">
-        <v>13.60833787918091</v>
+        <v>10.8449981212616</v>
       </c>
       <c r="J5" t="n">
-        <v>11.27579665184021</v>
+        <v>12.69704532623291</v>
       </c>
       <c r="K5" t="n">
-        <v>12.58541631698608</v>
+        <v>10.53482723236084</v>
       </c>
       <c r="L5" t="n">
-        <v>13.01964521408081</v>
+        <v>12.705921626091</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>16.25101017951965</v>
+        <v>13.28846478462219</v>
       </c>
       <c r="C6" t="n">
-        <v>13.34285807609558</v>
+        <v>11.55011057853699</v>
       </c>
       <c r="D6" t="n">
-        <v>13.85052275657654</v>
+        <v>14.90912985801697</v>
       </c>
       <c r="E6" t="n">
-        <v>16.52645778656006</v>
+        <v>11.50124263763428</v>
       </c>
       <c r="F6" t="n">
-        <v>13.8739013671875</v>
+        <v>16.34528970718384</v>
       </c>
       <c r="G6" t="n">
-        <v>15.09320974349976</v>
+        <v>14.83233499526978</v>
       </c>
       <c r="H6" t="n">
-        <v>13.90881299972534</v>
+        <v>14.68572807312012</v>
       </c>
       <c r="I6" t="n">
-        <v>12.64615201950073</v>
+        <v>11.31374454498291</v>
       </c>
       <c r="J6" t="n">
-        <v>18.30841588973999</v>
+        <v>11.56108283996582</v>
       </c>
       <c r="K6" t="n">
-        <v>14.02052664756775</v>
+        <v>12.34199547767639</v>
       </c>
       <c r="L6" t="n">
-        <v>14.78218674659729</v>
+        <v>13.23291234970093</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>13.84660911560059</v>
+        <v>12.56838965415955</v>
       </c>
       <c r="C7" t="n">
-        <v>10.66234540939331</v>
+        <v>15.23725271224976</v>
       </c>
       <c r="D7" t="n">
-        <v>16.46604752540588</v>
+        <v>11.90416359901428</v>
       </c>
       <c r="E7" t="n">
-        <v>12.87718343734741</v>
+        <v>11.82836818695068</v>
       </c>
       <c r="F7" t="n">
-        <v>14.44324684143066</v>
+        <v>11.20503616333008</v>
       </c>
       <c r="G7" t="n">
-        <v>11.94607591629028</v>
+        <v>11.63089632987976</v>
       </c>
       <c r="H7" t="n">
-        <v>11.7924702167511</v>
+        <v>15.92940163612366</v>
       </c>
       <c r="I7" t="n">
-        <v>12.85282564163208</v>
+        <v>15.74788689613342</v>
       </c>
       <c r="J7" t="n">
-        <v>15.50545907020569</v>
+        <v>15.7269434928894</v>
       </c>
       <c r="K7" t="n">
-        <v>12.08372378349304</v>
+        <v>12.21234083175659</v>
       </c>
       <c r="L7" t="n">
-        <v>13.24759869575501</v>
+        <v>13.39906795024872</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>12.12760400772095</v>
+        <v>17.26582765579224</v>
       </c>
       <c r="C8" t="n">
-        <v>12.42335796356201</v>
+        <v>16.52780151367188</v>
       </c>
       <c r="D8" t="n">
-        <v>11.82086157798767</v>
+        <v>13.77017593383789</v>
       </c>
       <c r="E8" t="n">
-        <v>12.32809114456177</v>
+        <v>12.07570719718933</v>
       </c>
       <c r="F8" t="n">
-        <v>11.36255288124084</v>
+        <v>11.12824010848999</v>
       </c>
       <c r="G8" t="n">
-        <v>14.43825840950012</v>
+        <v>15.67783260345459</v>
       </c>
       <c r="H8" t="n">
-        <v>12.56599950790405</v>
+        <v>15.22328972816467</v>
       </c>
       <c r="I8" t="n">
-        <v>15.22918319702148</v>
+        <v>11.1820969581604</v>
       </c>
       <c r="J8" t="n">
-        <v>11.69817972183228</v>
+        <v>12.04578733444214</v>
       </c>
       <c r="K8" t="n">
-        <v>13.11708426475525</v>
+        <v>15.37089538574219</v>
       </c>
       <c r="L8" t="n">
-        <v>12.71111726760864</v>
+        <v>14.02676544189453</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>13.99731135368347</v>
+        <v>11.28881096839905</v>
       </c>
       <c r="C9" t="n">
-        <v>11.22342705726624</v>
+        <v>11.96300864219666</v>
       </c>
       <c r="D9" t="n">
-        <v>15.6531138420105</v>
+        <v>12.04080104827881</v>
       </c>
       <c r="E9" t="n">
-        <v>13.65022373199463</v>
+        <v>10.95869374275208</v>
       </c>
       <c r="F9" t="n">
-        <v>12.40343976020813</v>
+        <v>13.45900774002075</v>
       </c>
       <c r="G9" t="n">
-        <v>13.06371974945068</v>
+        <v>11.70370149612427</v>
       </c>
       <c r="H9" t="n">
-        <v>11.13013100624084</v>
+        <v>12.36992049217224</v>
       </c>
       <c r="I9" t="n">
-        <v>13.20738697052002</v>
+        <v>12.18940281867981</v>
       </c>
       <c r="J9" t="n">
-        <v>13.64025473594666</v>
+        <v>12.10163807868958</v>
       </c>
       <c r="K9" t="n">
-        <v>14.45319104194641</v>
+        <v>12.59930729866028</v>
       </c>
       <c r="L9" t="n">
-        <v>13.24221992492676</v>
+        <v>12.06742923259735</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>15.34250950813293</v>
+        <v>11.72265148162842</v>
       </c>
       <c r="C10" t="n">
-        <v>12.7191367149353</v>
+        <v>16.65944886207581</v>
       </c>
       <c r="D10" t="n">
-        <v>14.05869817733765</v>
+        <v>11.94705104827881</v>
       </c>
       <c r="E10" t="n">
-        <v>18.5931396484375</v>
+        <v>16.11291122436523</v>
       </c>
       <c r="F10" t="n">
-        <v>14.02530312538147</v>
+        <v>10.93376064300537</v>
       </c>
       <c r="G10" t="n">
-        <v>12.03433632850647</v>
+        <v>11.61593699455261</v>
       </c>
       <c r="H10" t="n">
-        <v>14.77386546134949</v>
+        <v>12.28813910484314</v>
       </c>
       <c r="I10" t="n">
-        <v>16.72884511947632</v>
+        <v>11.09433174133301</v>
       </c>
       <c r="J10" t="n">
-        <v>12.27725672721863</v>
+        <v>16.10293769836426</v>
       </c>
       <c r="K10" t="n">
-        <v>12.76408314704895</v>
+        <v>13.0231671333313</v>
       </c>
       <c r="L10" t="n">
-        <v>14.33171739578247</v>
+        <v>13.1500335931778</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>16.86179757118225</v>
+        <v>13.43708467483521</v>
       </c>
       <c r="C11" t="n">
-        <v>12.95244193077087</v>
+        <v>16.27447867393494</v>
       </c>
       <c r="D11" t="n">
-        <v>14.08215427398682</v>
+        <v>12.06872606277466</v>
       </c>
       <c r="E11" t="n">
-        <v>11.86693811416626</v>
+        <v>11.76354146003723</v>
       </c>
       <c r="F11" t="n">
-        <v>12.23914766311646</v>
+        <v>14.65281510353088</v>
       </c>
       <c r="G11" t="n">
-        <v>17.27902460098267</v>
+        <v>12.06972312927246</v>
       </c>
       <c r="H11" t="n">
-        <v>19.02809262275696</v>
+        <v>12.61825633049011</v>
       </c>
       <c r="I11" t="n">
-        <v>12.87551665306091</v>
+        <v>12.93241691589355</v>
       </c>
       <c r="J11" t="n">
-        <v>13.67790293693542</v>
+        <v>12.11360549926758</v>
       </c>
       <c r="K11" t="n">
-        <v>16.28060388565063</v>
+        <v>12.76286959648132</v>
       </c>
       <c r="L11" t="n">
-        <v>14.71436202526093</v>
+        <v>13.06935174465179</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>17.27507448196411</v>
+        <v>12.56140875816345</v>
       </c>
       <c r="C12" t="n">
-        <v>15.15882706642151</v>
+        <v>11.95702362060547</v>
       </c>
       <c r="D12" t="n">
-        <v>17.77771377563477</v>
+        <v>15.15846300125122</v>
       </c>
       <c r="E12" t="n">
-        <v>15.8208281993866</v>
+        <v>11.92710494995117</v>
       </c>
       <c r="F12" t="n">
-        <v>17.47494959831238</v>
+        <v>14.69370579719543</v>
       </c>
       <c r="G12" t="n">
-        <v>13.81279039382935</v>
+        <v>15.7558650970459</v>
       </c>
       <c r="H12" t="n">
-        <v>14.63971304893494</v>
+        <v>16.15878844261169</v>
       </c>
       <c r="I12" t="n">
-        <v>12.83628797531128</v>
+        <v>11.98893880844116</v>
       </c>
       <c r="J12" t="n">
-        <v>13.23230648040771</v>
+        <v>17.1319899559021</v>
       </c>
       <c r="K12" t="n">
-        <v>20.0329225063324</v>
+        <v>12.22630476951599</v>
       </c>
       <c r="L12" t="n">
-        <v>15.8061413526535</v>
+        <v>13.95595932006836</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>13.48163437843323</v>
+        <v>13.29145574569702</v>
       </c>
       <c r="C13" t="n">
-        <v>16.75878214836121</v>
+        <v>19.41539573669434</v>
       </c>
       <c r="D13" t="n">
-        <v>14.30113673210144</v>
+        <v>14.99489903450012</v>
       </c>
       <c r="E13" t="n">
-        <v>17.87845587730408</v>
+        <v>15.07967400550842</v>
       </c>
       <c r="F13" t="n">
-        <v>14.53648948669434</v>
+        <v>14.23194074630737</v>
       </c>
       <c r="G13" t="n">
-        <v>14.71202802658081</v>
+        <v>13.77816200256348</v>
       </c>
       <c r="H13" t="n">
-        <v>12.99294376373291</v>
+        <v>14.61092686653137</v>
       </c>
       <c r="I13" t="n">
-        <v>14.08616614341736</v>
+        <v>12.60130167007446</v>
       </c>
       <c r="J13" t="n">
-        <v>15.76783108711243</v>
+        <v>15.8605854511261</v>
       </c>
       <c r="K13" t="n">
-        <v>17.48493313789368</v>
+        <v>15.11757206916809</v>
       </c>
       <c r="L13" t="n">
-        <v>15.20004007816315</v>
+        <v>14.89819133281708</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>17.01078224182129</v>
+        <v>12.42178249359131</v>
       </c>
       <c r="C14" t="n">
-        <v>12.97076535224915</v>
+        <v>15.41078782081604</v>
       </c>
       <c r="D14" t="n">
-        <v>16.01338338851929</v>
+        <v>11.90715742111206</v>
       </c>
       <c r="E14" t="n">
-        <v>17.82266521453857</v>
+        <v>17.72360372543335</v>
       </c>
       <c r="F14" t="n">
-        <v>12.66008043289185</v>
+        <v>14.23393559455872</v>
       </c>
       <c r="G14" t="n">
-        <v>13.78113746643066</v>
+        <v>12.23428297042847</v>
       </c>
       <c r="H14" t="n">
-        <v>16.02450251579285</v>
+        <v>11.71766495704651</v>
       </c>
       <c r="I14" t="n">
-        <v>13.3734188079834</v>
+        <v>13.71831393241882</v>
       </c>
       <c r="J14" t="n">
-        <v>14.09263396263123</v>
+        <v>12.49059677124023</v>
       </c>
       <c r="K14" t="n">
-        <v>12.96847248077393</v>
+        <v>15.91045188903809</v>
       </c>
       <c r="L14" t="n">
-        <v>14.67178418636322</v>
+        <v>13.77685775756836</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>16.85006284713745</v>
+        <v>15.30018544197083</v>
       </c>
       <c r="C15" t="n">
-        <v>15.01887893676758</v>
+        <v>12.94338607788086</v>
       </c>
       <c r="D15" t="n">
-        <v>15.16042280197144</v>
+        <v>11.88022994995117</v>
       </c>
       <c r="E15" t="n">
-        <v>11.41131925582886</v>
+        <v>15.1594603061676</v>
       </c>
       <c r="F15" t="n">
-        <v>14.47383117675781</v>
+        <v>13.27649617195129</v>
       </c>
       <c r="G15" t="n">
-        <v>15.33958053588867</v>
+        <v>12.3459837436676</v>
       </c>
       <c r="H15" t="n">
-        <v>16.51755046844482</v>
+        <v>11.98295521736145</v>
       </c>
       <c r="I15" t="n">
-        <v>10.98189973831177</v>
+        <v>11.77750515937805</v>
       </c>
       <c r="J15" t="n">
-        <v>14.56960129737854</v>
+        <v>11.53116297721863</v>
       </c>
       <c r="K15" t="n">
-        <v>13.50738668441772</v>
+        <v>11.63987255096436</v>
       </c>
       <c r="L15" t="n">
-        <v>14.38305337429047</v>
+        <v>12.78372375965118</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>12.2751145362854</v>
+        <v>10.71734023094177</v>
       </c>
       <c r="C16" t="n">
-        <v>17.80471658706665</v>
+        <v>12.03780817985535</v>
       </c>
       <c r="D16" t="n">
-        <v>12.96175813674927</v>
+        <v>11.82737135887146</v>
       </c>
       <c r="E16" t="n">
-        <v>12.9667763710022</v>
+        <v>12.66413331031799</v>
       </c>
       <c r="F16" t="n">
-        <v>13.29990005493164</v>
+        <v>14.41046380996704</v>
       </c>
       <c r="G16" t="n">
-        <v>14.44344258308411</v>
+        <v>12.46067786216736</v>
       </c>
       <c r="H16" t="n">
-        <v>15.06779146194458</v>
+        <v>12.42976045608521</v>
       </c>
       <c r="I16" t="n">
-        <v>12.44113302230835</v>
+        <v>15.75486898422241</v>
       </c>
       <c r="J16" t="n">
-        <v>12.20268869400024</v>
+        <v>11.52817130088806</v>
       </c>
       <c r="K16" t="n">
-        <v>12.15287780761719</v>
+        <v>12.27317976951599</v>
       </c>
       <c r="L16" t="n">
-        <v>13.56161992549896</v>
+        <v>12.61037752628326</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>15.44584584236145</v>
+        <v>10.61860418319702</v>
       </c>
       <c r="C17" t="n">
-        <v>13.81408715248108</v>
+        <v>16.86789226531982</v>
       </c>
       <c r="D17" t="n">
-        <v>14.69785618782043</v>
+        <v>10.72731304168701</v>
       </c>
       <c r="E17" t="n">
-        <v>15.44481825828552</v>
+        <v>14.68273544311523</v>
       </c>
       <c r="F17" t="n">
-        <v>12.38679671287537</v>
+        <v>14.82236194610596</v>
       </c>
       <c r="G17" t="n">
-        <v>15.85775709152222</v>
+        <v>14.93313646316528</v>
       </c>
       <c r="H17" t="n">
-        <v>14.64088487625122</v>
+        <v>13.25754642486572</v>
       </c>
       <c r="I17" t="n">
-        <v>13.21209311485291</v>
+        <v>16.33531546592712</v>
       </c>
       <c r="J17" t="n">
-        <v>14.97487211227417</v>
+        <v>11.75057625770569</v>
       </c>
       <c r="K17" t="n">
-        <v>13.19685459136963</v>
+        <v>11.75157332420349</v>
       </c>
       <c r="L17" t="n">
-        <v>14.3671865940094</v>
+        <v>13.57470548152924</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>14.15444493293762</v>
+        <v>14.68672466278076</v>
       </c>
       <c r="C18" t="n">
-        <v>14.60081768035889</v>
+        <v>16.37620663642883</v>
       </c>
       <c r="D18" t="n">
-        <v>12.24381065368652</v>
+        <v>11.44638991355896</v>
       </c>
       <c r="E18" t="n">
-        <v>11.81487083435059</v>
+        <v>16.52879905700684</v>
       </c>
       <c r="F18" t="n">
-        <v>15.72744560241699</v>
+        <v>13.67842054367065</v>
       </c>
       <c r="G18" t="n">
-        <v>12.91362190246582</v>
+        <v>14.82535481452942</v>
       </c>
       <c r="H18" t="n">
-        <v>13.48063492774963</v>
+        <v>11.99990963935852</v>
       </c>
       <c r="I18" t="n">
-        <v>16.74646615982056</v>
+        <v>12.23727488517761</v>
       </c>
       <c r="J18" t="n">
-        <v>15.93551182746887</v>
+        <v>11.89718437194824</v>
       </c>
       <c r="K18" t="n">
-        <v>12.61983227729797</v>
+        <v>14.18706059455872</v>
       </c>
       <c r="L18" t="n">
-        <v>14.02374567985535</v>
+        <v>13.78633251190186</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>13.55001497268677</v>
+        <v>16.44402503967285</v>
       </c>
       <c r="C19" t="n">
-        <v>11.4851405620575</v>
+        <v>11.30975604057312</v>
       </c>
       <c r="D19" t="n">
-        <v>16.77476668357849</v>
+        <v>12.24824547767639</v>
       </c>
       <c r="E19" t="n">
-        <v>17.5991358757019</v>
+        <v>12.14551997184753</v>
       </c>
       <c r="F19" t="n">
-        <v>16.82820963859558</v>
+        <v>12.14552116394043</v>
       </c>
       <c r="G19" t="n">
-        <v>14.20556092262268</v>
+        <v>14.3366596698761</v>
       </c>
       <c r="H19" t="n">
-        <v>15.12496304512024</v>
+        <v>16.19967937469482</v>
       </c>
       <c r="I19" t="n">
-        <v>11.96955466270447</v>
+        <v>14.09131669998169</v>
       </c>
       <c r="J19" t="n">
-        <v>11.4697642326355</v>
+        <v>11.70569682121277</v>
       </c>
       <c r="K19" t="n">
-        <v>13.46768975257874</v>
+        <v>11.99492335319519</v>
       </c>
       <c r="L19" t="n">
-        <v>14.24748003482819</v>
+        <v>13.26213436126709</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>13.27566242218018</v>
+        <v>14.49723172187805</v>
       </c>
       <c r="C20" t="n">
-        <v>14.49459004402161</v>
+        <v>11.60297107696533</v>
       </c>
       <c r="D20" t="n">
-        <v>10.86930847167969</v>
+        <v>12.12956285476685</v>
       </c>
       <c r="E20" t="n">
-        <v>12.69714188575745</v>
+        <v>11.41347765922546</v>
       </c>
       <c r="F20" t="n">
-        <v>13.72851014137268</v>
+        <v>11.14519548416138</v>
       </c>
       <c r="G20" t="n">
-        <v>11.91162085533142</v>
+        <v>10.83302998542786</v>
       </c>
       <c r="H20" t="n">
-        <v>15.6202347278595</v>
+        <v>11.04945111274719</v>
       </c>
       <c r="I20" t="n">
-        <v>14.91347789764404</v>
+        <v>10.59865736961365</v>
       </c>
       <c r="J20" t="n">
-        <v>15.08206176757812</v>
+        <v>10.38921666145325</v>
       </c>
       <c r="K20" t="n">
-        <v>11.58100891113281</v>
+        <v>11.82138729095459</v>
       </c>
       <c r="L20" t="n">
-        <v>13.41736171245575</v>
+        <v>11.54801812171936</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>13.03479957580566</v>
+        <v>12.45469331741333</v>
       </c>
       <c r="C21" t="n">
-        <v>15.27257180213928</v>
+        <v>12.27417659759521</v>
       </c>
       <c r="D21" t="n">
-        <v>15.03177094459534</v>
+        <v>12.24325919151306</v>
       </c>
       <c r="E21" t="n">
-        <v>14.26862239837646</v>
+        <v>12.4846134185791</v>
       </c>
       <c r="F21" t="n">
-        <v>16.3628396987915</v>
+        <v>16.30048084259033</v>
       </c>
       <c r="G21" t="n">
-        <v>12.02041172981262</v>
+        <v>11.84133434295654</v>
       </c>
       <c r="H21" t="n">
-        <v>11.91717267036438</v>
+        <v>15.12654829025269</v>
       </c>
       <c r="I21" t="n">
-        <v>15.81229305267334</v>
+        <v>11.96600079536438</v>
       </c>
       <c r="J21" t="n">
-        <v>15.08159065246582</v>
+        <v>13.39717388153076</v>
       </c>
       <c r="K21" t="n">
-        <v>14.63470649719238</v>
+        <v>11.5580906867981</v>
       </c>
       <c r="L21" t="n">
-        <v>14.34367790222168</v>
+        <v>12.96463713645935</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>14.30307507514954</v>
+        <v>12.42676830291748</v>
       </c>
       <c r="C22" t="n">
-        <v>14.70900225639343</v>
+        <v>15.66248536109924</v>
       </c>
       <c r="D22" t="n">
-        <v>15.17083930969238</v>
+        <v>14.97994089126587</v>
       </c>
       <c r="E22" t="n">
-        <v>12.99092531204224</v>
+        <v>16.40812158584595</v>
       </c>
       <c r="F22" t="n">
-        <v>13.19885063171387</v>
+        <v>15.18339586257935</v>
       </c>
       <c r="G22" t="n">
-        <v>13.00883865356445</v>
+        <v>12.67011737823486</v>
       </c>
       <c r="H22" t="n">
-        <v>13.61927628517151</v>
+        <v>17.41443014144897</v>
       </c>
       <c r="I22" t="n">
-        <v>12.03433132171631</v>
+        <v>12.75887942314148</v>
       </c>
       <c r="J22" t="n">
-        <v>13.1983642578125</v>
+        <v>13.79610705375671</v>
       </c>
       <c r="K22" t="n">
-        <v>16.71890997886658</v>
+        <v>13.11393046379089</v>
       </c>
       <c r="L22" t="n">
-        <v>13.89524130821228</v>
+        <v>14.44141764640808</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>10.7700457572937</v>
+        <v>12.66213893890381</v>
       </c>
       <c r="C23" t="n">
-        <v>13.20735812187195</v>
+        <v>11.42245388031006</v>
       </c>
       <c r="D23" t="n">
-        <v>13.32254719734192</v>
+        <v>11.07338714599609</v>
       </c>
       <c r="E23" t="n">
-        <v>16.64667153358459</v>
+        <v>12.14851260185242</v>
       </c>
       <c r="F23" t="n">
-        <v>15.5718400478363</v>
+        <v>15.42674517631531</v>
       </c>
       <c r="G23" t="n">
-        <v>14.43423414230347</v>
+        <v>13.5547513961792</v>
       </c>
       <c r="H23" t="n">
-        <v>18.87619161605835</v>
+        <v>11.05942535400391</v>
       </c>
       <c r="I23" t="n">
-        <v>18.52863025665283</v>
+        <v>11.12325382232666</v>
       </c>
       <c r="J23" t="n">
-        <v>17.56394267082214</v>
+        <v>11.28282737731934</v>
       </c>
       <c r="K23" t="n">
-        <v>14.94941973686218</v>
+        <v>11.5491156578064</v>
       </c>
       <c r="L23" t="n">
-        <v>15.38708810806274</v>
+        <v>12.13026113510132</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>19.84197592735291</v>
+        <v>11.78049683570862</v>
       </c>
       <c r="C24" t="n">
-        <v>14.30100870132446</v>
+        <v>14.69869232177734</v>
       </c>
       <c r="D24" t="n">
-        <v>12.58740401268005</v>
+        <v>14.9141161441803</v>
       </c>
       <c r="E24" t="n">
-        <v>14.89557552337646</v>
+        <v>12.42477369308472</v>
       </c>
       <c r="F24" t="n">
-        <v>17.82865333557129</v>
+        <v>15.94835042953491</v>
       </c>
       <c r="G24" t="n">
-        <v>12.37400484085083</v>
+        <v>11.15118026733398</v>
       </c>
       <c r="H24" t="n">
-        <v>16.55333185195923</v>
+        <v>12.14552021026611</v>
       </c>
       <c r="I24" t="n">
-        <v>14.09757494926453</v>
+        <v>13.45402145385742</v>
       </c>
       <c r="J24" t="n">
-        <v>12.32210302352905</v>
+        <v>14.61591410636902</v>
       </c>
       <c r="K24" t="n">
-        <v>17.35925674438477</v>
+        <v>11.96600103378296</v>
       </c>
       <c r="L24" t="n">
-        <v>15.21608889102936</v>
+        <v>13.30990664958954</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>14.72603034973145</v>
+        <v>12.46566462516785</v>
       </c>
       <c r="C25" t="n">
-        <v>12.70608186721802</v>
+        <v>13.93573236465454</v>
       </c>
       <c r="D25" t="n">
-        <v>13.80606889724731</v>
+        <v>14.56505107879639</v>
       </c>
       <c r="E25" t="n">
-        <v>16.21385216712952</v>
+        <v>16.29442453384399</v>
       </c>
       <c r="F25" t="n">
-        <v>14.54068160057068</v>
+        <v>14.00853776931763</v>
       </c>
       <c r="G25" t="n">
-        <v>17.36032485961914</v>
+        <v>20.25483465194702</v>
       </c>
       <c r="H25" t="n">
-        <v>16.06225848197937</v>
+        <v>17.81735229492188</v>
       </c>
       <c r="I25" t="n">
-        <v>14.65265107154846</v>
+        <v>12.92044830322266</v>
       </c>
       <c r="J25" t="n">
-        <v>13.44327855110168</v>
+        <v>13.49491214752197</v>
       </c>
       <c r="K25" t="n">
-        <v>18.77167749404907</v>
+        <v>13.96066617965698</v>
       </c>
       <c r="L25" t="n">
-        <v>15.22829053401947</v>
+        <v>14.97176239490509</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>11.65329432487488</v>
+        <v>11.81141328811646</v>
       </c>
       <c r="C26" t="n">
-        <v>12.17902803421021</v>
+        <v>10.68243265151978</v>
       </c>
       <c r="D26" t="n">
-        <v>11.19745564460754</v>
+        <v>10.8689341545105</v>
       </c>
       <c r="E26" t="n">
-        <v>11.33663749694824</v>
+        <v>13.79102683067322</v>
       </c>
       <c r="F26" t="n">
-        <v>10.70471906661987</v>
+        <v>11.08934545516968</v>
       </c>
       <c r="G26" t="n">
-        <v>13.11611366271973</v>
+        <v>10.87292265892029</v>
       </c>
       <c r="H26" t="n">
-        <v>11.56255006790161</v>
+        <v>12.66772365570068</v>
       </c>
       <c r="I26" t="n">
-        <v>10.86131167411804</v>
+        <v>10.04912638664246</v>
       </c>
       <c r="J26" t="n">
-        <v>12.05755972862244</v>
+        <v>10.56674289703369</v>
       </c>
       <c r="K26" t="n">
-        <v>13.28292846679688</v>
+        <v>13.61160016059875</v>
       </c>
       <c r="L26" t="n">
-        <v>11.79515981674194</v>
+        <v>11.60112681388855</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>20.31100368499756</v>
+        <v>12.45070385932922</v>
       </c>
       <c r="C27" t="n">
-        <v>12.65277409553528</v>
+        <v>12.08568000793457</v>
       </c>
       <c r="D27" t="n">
-        <v>12.66869854927063</v>
+        <v>11.60895490646362</v>
       </c>
       <c r="E27" t="n">
-        <v>13.93003153800964</v>
+        <v>13.15681576728821</v>
       </c>
       <c r="F27" t="n">
-        <v>15.3603732585907</v>
+        <v>12.84863901138306</v>
       </c>
       <c r="G27" t="n">
-        <v>12.26527166366577</v>
+        <v>11.67079019546509</v>
       </c>
       <c r="H27" t="n">
-        <v>12.08618545532227</v>
+        <v>12.21732759475708</v>
       </c>
       <c r="I27" t="n">
-        <v>12.37050914764404</v>
+        <v>16.40812134742737</v>
       </c>
       <c r="J27" t="n">
-        <v>13.98487544059753</v>
+        <v>12.61526441574097</v>
       </c>
       <c r="K27" t="n">
-        <v>13.23731589317322</v>
+        <v>14.94403719902039</v>
       </c>
       <c r="L27" t="n">
-        <v>13.88670387268066</v>
+        <v>13.00063343048096</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>13.5154345035553</v>
+        <v>15.75486826896667</v>
       </c>
       <c r="C28" t="n">
-        <v>14.8514096736908</v>
+        <v>12.34099769592285</v>
       </c>
       <c r="D28" t="n">
-        <v>12.32646322250366</v>
+        <v>13.87988257408142</v>
       </c>
       <c r="E28" t="n">
-        <v>14.80898976325989</v>
+        <v>12.28115749359131</v>
       </c>
       <c r="F28" t="n">
-        <v>12.45912384986877</v>
+        <v>11.84731769561768</v>
       </c>
       <c r="G28" t="n">
-        <v>16.24119997024536</v>
+        <v>12.79578137397766</v>
       </c>
       <c r="H28" t="n">
-        <v>12.11021947860718</v>
+        <v>11.26687002182007</v>
       </c>
       <c r="I28" t="n">
-        <v>12.6782329082489</v>
+        <v>13.93074560165405</v>
       </c>
       <c r="J28" t="n">
-        <v>12.86621522903442</v>
+        <v>11.50224041938782</v>
       </c>
       <c r="K28" t="n">
-        <v>12.33207488059998</v>
+        <v>11.41048550605774</v>
       </c>
       <c r="L28" t="n">
-        <v>13.41893634796143</v>
+        <v>12.70103466510773</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>12.83781599998474</v>
+        <v>11.30377197265625</v>
       </c>
       <c r="C29" t="n">
-        <v>11.28723502159119</v>
+        <v>10.95669960975647</v>
       </c>
       <c r="D29" t="n">
-        <v>11.36315989494324</v>
+        <v>10.98263001441956</v>
       </c>
       <c r="E29" t="n">
-        <v>12.74932050704956</v>
+        <v>11.86128115653992</v>
       </c>
       <c r="F29" t="n">
-        <v>11.13350749015808</v>
+        <v>11.47473978996277</v>
       </c>
       <c r="G29" t="n">
-        <v>12.04863905906677</v>
+        <v>11.035489320755</v>
       </c>
       <c r="H29" t="n">
-        <v>13.97211670875549</v>
+        <v>11.39353108406067</v>
       </c>
       <c r="I29" t="n">
-        <v>11.91247916221619</v>
+        <v>10.48097109794617</v>
       </c>
       <c r="J29" t="n">
-        <v>11.7804229259491</v>
+        <v>10.97664642333984</v>
       </c>
       <c r="K29" t="n">
-        <v>11.93146061897278</v>
+        <v>10.12093448638916</v>
       </c>
       <c r="L29" t="n">
-        <v>12.10161573886871</v>
+        <v>11.05866949558258</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>15.59538984298706</v>
+        <v>15.3180365562439</v>
       </c>
       <c r="C30" t="n">
-        <v>11.52947950363159</v>
+        <v>14.46631550788879</v>
       </c>
       <c r="D30" t="n">
-        <v>13.96218180656433</v>
+        <v>11.92311477661133</v>
       </c>
       <c r="E30" t="n">
-        <v>11.18986749649048</v>
+        <v>11.41846489906311</v>
       </c>
       <c r="F30" t="n">
-        <v>11.42728972434998</v>
+        <v>15.12155699729919</v>
       </c>
       <c r="G30" t="n">
-        <v>11.53149700164795</v>
+        <v>11.96699786186218</v>
       </c>
       <c r="H30" t="n">
-        <v>13.80909705162048</v>
+        <v>11.67477941513062</v>
       </c>
       <c r="I30" t="n">
-        <v>11.19301795959473</v>
+        <v>14.08732724189758</v>
       </c>
       <c r="J30" t="n">
-        <v>12.34340357780457</v>
+        <v>15.73591923713684</v>
       </c>
       <c r="K30" t="n">
-        <v>13.79112720489502</v>
+        <v>12.80675172805786</v>
       </c>
       <c r="L30" t="n">
-        <v>12.63723511695862</v>
+        <v>13.45192642211914</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>14.5486273765564</v>
+        <v>17.00951170921326</v>
       </c>
       <c r="C31" t="n">
-        <v>13.72780728340149</v>
+        <v>11.53914260864258</v>
       </c>
       <c r="D31" t="n">
-        <v>15.58647608757019</v>
+        <v>16.78106689453125</v>
       </c>
       <c r="E31" t="n">
-        <v>17.46153259277344</v>
+        <v>11.61194801330566</v>
       </c>
       <c r="F31" t="n">
-        <v>12.12794065475464</v>
+        <v>12.23978281021118</v>
       </c>
       <c r="G31" t="n">
-        <v>17.78781914710999</v>
+        <v>12.99425101280212</v>
       </c>
       <c r="H31" t="n">
-        <v>12.337641954422</v>
+        <v>12.49658155441284</v>
       </c>
       <c r="I31" t="n">
-        <v>16.41234183311462</v>
+        <v>11.57704043388367</v>
       </c>
       <c r="J31" t="n">
-        <v>11.6822304725647</v>
+        <v>15.22927355766296</v>
       </c>
       <c r="K31" t="n">
-        <v>12.5709867477417</v>
+        <v>12.46765923500061</v>
       </c>
       <c r="L31" t="n">
-        <v>14.42434041500092</v>
+        <v>13.39462578296661</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>12.0323600769043</v>
+        <v>15.62621212005615</v>
       </c>
       <c r="C32" t="n">
-        <v>11.27974581718445</v>
+        <v>11.95901870727539</v>
       </c>
       <c r="D32" t="n">
-        <v>16.36182403564453</v>
+        <v>11.88920593261719</v>
       </c>
       <c r="E32" t="n">
-        <v>13.79339623451233</v>
+        <v>15.64915108680725</v>
       </c>
       <c r="F32" t="n">
-        <v>13.01182985305786</v>
+        <v>11.67178678512573</v>
       </c>
       <c r="G32" t="n">
-        <v>12.32527685165405</v>
+        <v>14.44537019729614</v>
       </c>
       <c r="H32" t="n">
-        <v>11.34200429916382</v>
+        <v>12.38089060783386</v>
       </c>
       <c r="I32" t="n">
-        <v>11.88858389854431</v>
+        <v>14.83931684494019</v>
       </c>
       <c r="J32" t="n">
-        <v>11.75391936302185</v>
+        <v>12.67410707473755</v>
       </c>
       <c r="K32" t="n">
-        <v>15.05085444450378</v>
+        <v>11.60597085952759</v>
       </c>
       <c r="L32" t="n">
-        <v>12.88397948741913</v>
+        <v>13.2741030216217</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>13.26850199699402</v>
+        <v>13.15681624412537</v>
       </c>
       <c r="C33" t="n">
-        <v>13.35296869277954</v>
+        <v>11.93907237052917</v>
       </c>
       <c r="D33" t="n">
-        <v>11.45580005645752</v>
+        <v>17.01449990272522</v>
       </c>
       <c r="E33" t="n">
-        <v>12.36307549476624</v>
+        <v>16.27348065376282</v>
       </c>
       <c r="F33" t="n">
-        <v>15.43267822265625</v>
+        <v>11.90516304969788</v>
       </c>
       <c r="G33" t="n">
-        <v>12.5315797328949</v>
+        <v>15.35394048690796</v>
       </c>
       <c r="H33" t="n">
-        <v>12.12861299514771</v>
+        <v>15.2980899810791</v>
       </c>
       <c r="I33" t="n">
-        <v>12.56302499771118</v>
+        <v>11.97298216819763</v>
       </c>
       <c r="J33" t="n">
-        <v>11.97497844696045</v>
+        <v>12.27716684341431</v>
       </c>
       <c r="K33" t="n">
-        <v>19.46539449691772</v>
+        <v>11.93608117103577</v>
       </c>
       <c r="L33" t="n">
-        <v>13.45366151332855</v>
+        <v>13.71272928714752</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>12.83828043937683</v>
+        <v>14.44836187362671</v>
       </c>
       <c r="C34" t="n">
-        <v>11.21540713310242</v>
+        <v>11.25689721107483</v>
       </c>
       <c r="D34" t="n">
-        <v>11.50818467140198</v>
+        <v>12.6591465473175</v>
       </c>
       <c r="E34" t="n">
-        <v>12.40040683746338</v>
+        <v>10.89586305618286</v>
       </c>
       <c r="F34" t="n">
-        <v>13.28420639038086</v>
+        <v>11.32870388031006</v>
       </c>
       <c r="G34" t="n">
-        <v>11.99042844772339</v>
+        <v>10.67644882202148</v>
       </c>
       <c r="H34" t="n">
-        <v>11.09024882316589</v>
+        <v>13.49191999435425</v>
       </c>
       <c r="I34" t="n">
-        <v>11.79841732978821</v>
+        <v>10.76521229743958</v>
       </c>
       <c r="J34" t="n">
-        <v>12.44889569282532</v>
+        <v>11.33469724655151</v>
       </c>
       <c r="K34" t="n">
-        <v>11.94406342506409</v>
+        <v>10.81906747817993</v>
       </c>
       <c r="L34" t="n">
-        <v>12.05185391902924</v>
+        <v>11.76763184070587</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>12.02640414237976</v>
+        <v>11.63688158988953</v>
       </c>
       <c r="C35" t="n">
-        <v>12.07775235176086</v>
+        <v>13.57469820976257</v>
       </c>
       <c r="D35" t="n">
-        <v>11.60690498352051</v>
+        <v>11.52019238471985</v>
       </c>
       <c r="E35" t="n">
-        <v>16.3548424243927</v>
+        <v>11.73461937904358</v>
       </c>
       <c r="F35" t="n">
-        <v>15.3134937286377</v>
+        <v>19.06302213668823</v>
       </c>
       <c r="G35" t="n">
-        <v>17.4889440536499</v>
+        <v>14.9300742149353</v>
       </c>
       <c r="H35" t="n">
-        <v>17.3283953666687</v>
+        <v>11.53016519546509</v>
       </c>
       <c r="I35" t="n">
-        <v>14.69954705238342</v>
+        <v>11.45636391639709</v>
       </c>
       <c r="J35" t="n">
-        <v>12.69125890731812</v>
+        <v>16.41011619567871</v>
       </c>
       <c r="K35" t="n">
-        <v>12.08023929595947</v>
+        <v>12.88354659080505</v>
       </c>
       <c r="L35" t="n">
-        <v>14.16677823066711</v>
+        <v>13.4739679813385</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>12.99487948417664</v>
+        <v>13.04062366485596</v>
       </c>
       <c r="C36" t="n">
-        <v>12.94054579734802</v>
+        <v>11.24692296981812</v>
       </c>
       <c r="D36" t="n">
-        <v>12.24278616905212</v>
+        <v>12.3001070022583</v>
       </c>
       <c r="E36" t="n">
-        <v>15.09304618835449</v>
+        <v>12.11659812927246</v>
       </c>
       <c r="F36" t="n">
-        <v>15.78328442573547</v>
+        <v>15.80074524879456</v>
       </c>
       <c r="G36" t="n">
-        <v>13.51409935951233</v>
+        <v>11.48129725456238</v>
       </c>
       <c r="H36" t="n">
-        <v>13.30865454673767</v>
+        <v>12.6890664100647</v>
       </c>
       <c r="I36" t="n">
-        <v>11.84383225440979</v>
+        <v>11.51819729804993</v>
       </c>
       <c r="J36" t="n">
-        <v>13.63031959533691</v>
+        <v>12.19638395309448</v>
       </c>
       <c r="K36" t="n">
-        <v>13.56999540328979</v>
+        <v>12.73294925689697</v>
       </c>
       <c r="L36" t="n">
-        <v>13.49214432239532</v>
+        <v>12.51228911876678</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>12.35384893417358</v>
+        <v>10.52485394477844</v>
       </c>
       <c r="C37" t="n">
-        <v>15.2632942199707</v>
+        <v>12.313072681427</v>
       </c>
       <c r="D37" t="n">
-        <v>12.72310090065002</v>
+        <v>11.24592542648315</v>
       </c>
       <c r="E37" t="n">
-        <v>11.66327691078186</v>
+        <v>14.59397268295288</v>
       </c>
       <c r="F37" t="n">
-        <v>12.27788138389587</v>
+        <v>15.93339109420776</v>
       </c>
       <c r="G37" t="n">
-        <v>12.47224378585815</v>
+        <v>14.01452159881592</v>
       </c>
       <c r="H37" t="n">
-        <v>12.41934704780579</v>
+        <v>11.54811763763428</v>
       </c>
       <c r="I37" t="n">
-        <v>11.24337649345398</v>
+        <v>11.1212592124939</v>
       </c>
       <c r="J37" t="n">
-        <v>12.72809743881226</v>
+        <v>10.77618288993835</v>
       </c>
       <c r="K37" t="n">
-        <v>11.53960061073303</v>
+        <v>12.19239544868469</v>
       </c>
       <c r="L37" t="n">
-        <v>12.46840677261353</v>
+        <v>12.42636926174164</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>16.89894032478333</v>
+        <v>14.88619112968445</v>
       </c>
       <c r="C38" t="n">
-        <v>15.77980303764343</v>
+        <v>14.66877269744873</v>
       </c>
       <c r="D38" t="n">
-        <v>12.03333115577698</v>
+        <v>12.54744553565979</v>
       </c>
       <c r="E38" t="n">
-        <v>18.82739520072937</v>
+        <v>12.15449619293213</v>
       </c>
       <c r="F38" t="n">
-        <v>15.829669713974</v>
+        <v>12.37988233566284</v>
       </c>
       <c r="G38" t="n">
-        <v>15.94598007202148</v>
+        <v>11.85529661178589</v>
       </c>
       <c r="H38" t="n">
-        <v>11.70713996887207</v>
+        <v>14.55507683753967</v>
       </c>
       <c r="I38" t="n">
-        <v>13.19736933708191</v>
+        <v>14.24590444564819</v>
       </c>
       <c r="J38" t="n">
-        <v>12.85725069046021</v>
+        <v>11.73761081695557</v>
       </c>
       <c r="K38" t="n">
-        <v>13.1484911441803</v>
+        <v>17.15213108062744</v>
       </c>
       <c r="L38" t="n">
-        <v>14.62253706455231</v>
+        <v>13.61828076839447</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>13.78037571907043</v>
+        <v>10.53383040428162</v>
       </c>
       <c r="C39" t="n">
-        <v>13.78087472915649</v>
+        <v>10.22665166854858</v>
       </c>
       <c r="D39" t="n">
-        <v>11.51019811630249</v>
+        <v>11.30077934265137</v>
       </c>
       <c r="E39" t="n">
-        <v>13.03082275390625</v>
+        <v>9.754914045333862</v>
       </c>
       <c r="F39" t="n">
-        <v>12.04129552841187</v>
+        <v>10.35032153129578</v>
       </c>
       <c r="G39" t="n">
-        <v>11.45978331565857</v>
+        <v>10.6136167049408</v>
       </c>
       <c r="H39" t="n">
-        <v>10.92531704902649</v>
+        <v>10.61461472511292</v>
       </c>
       <c r="I39" t="n">
-        <v>10.2189610004425</v>
+        <v>11.34865045547485</v>
       </c>
       <c r="J39" t="n">
-        <v>10.64888405799866</v>
+        <v>11.08834433555603</v>
       </c>
       <c r="K39" t="n">
-        <v>12.44626593589783</v>
+        <v>10.50191593170166</v>
       </c>
       <c r="L39" t="n">
-        <v>11.98427782058716</v>
+        <v>10.63336391448975</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>16.02923703193665</v>
+        <v>12.58135461807251</v>
       </c>
       <c r="C40" t="n">
-        <v>15.57834458351135</v>
+        <v>11.90815472602844</v>
       </c>
       <c r="D40" t="n">
-        <v>14.85815572738647</v>
+        <v>13.28846430778503</v>
       </c>
       <c r="E40" t="n">
-        <v>17.26803922653198</v>
+        <v>12.47264528274536</v>
       </c>
       <c r="F40" t="n">
-        <v>17.34329986572266</v>
+        <v>12.4237756729126</v>
       </c>
       <c r="G40" t="n">
-        <v>18.19368028640747</v>
+        <v>15.87360095977783</v>
       </c>
       <c r="H40" t="n">
-        <v>18.89783000946045</v>
+        <v>11.9051628112793</v>
       </c>
       <c r="I40" t="n">
-        <v>12.97893571853638</v>
+        <v>13.21665620803833</v>
       </c>
       <c r="J40" t="n">
-        <v>13.99406218528748</v>
+        <v>12.03134083747864</v>
       </c>
       <c r="K40" t="n">
-        <v>13.16573929786682</v>
+        <v>12.21932291984558</v>
       </c>
       <c r="L40" t="n">
-        <v>15.83073239326477</v>
+        <v>12.79204783439636</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>14.34916973114014</v>
+        <v>14.95999360084534</v>
       </c>
       <c r="C41" t="n">
-        <v>15.0346794128418</v>
+        <v>11.13621878623962</v>
       </c>
       <c r="D41" t="n">
-        <v>12.7774510383606</v>
+        <v>11.53415465354919</v>
       </c>
       <c r="E41" t="n">
-        <v>10.56756472587585</v>
+        <v>10.30743646621704</v>
       </c>
       <c r="F41" t="n">
-        <v>10.13269829750061</v>
+        <v>10.42013382911682</v>
       </c>
       <c r="G41" t="n">
-        <v>12.47467446327209</v>
+        <v>11.16913199424744</v>
       </c>
       <c r="H41" t="n">
-        <v>11.20733213424683</v>
+        <v>11.16414451599121</v>
       </c>
       <c r="I41" t="n">
-        <v>11.15199518203735</v>
+        <v>13.08101868629456</v>
       </c>
       <c r="J41" t="n">
-        <v>13.94420576095581</v>
+        <v>14.89915657043457</v>
       </c>
       <c r="K41" t="n">
-        <v>13.75025343894958</v>
+        <v>10.87092757225037</v>
       </c>
       <c r="L41" t="n">
-        <v>12.53900241851807</v>
+        <v>11.95423166751862</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>13.36892867088318</v>
+        <v>15.13053703308105</v>
       </c>
       <c r="C42" t="n">
-        <v>11.48682141304016</v>
+        <v>14.18905568122864</v>
       </c>
       <c r="D42" t="n">
-        <v>15.95004796981812</v>
+        <v>11.77451181411743</v>
       </c>
       <c r="E42" t="n">
-        <v>12.43534278869629</v>
+        <v>15.17142844200134</v>
       </c>
       <c r="F42" t="n">
-        <v>13.33158612251282</v>
+        <v>14.68373227119446</v>
       </c>
       <c r="G42" t="n">
-        <v>12.67522811889648</v>
+        <v>11.91314148902893</v>
       </c>
       <c r="H42" t="n">
-        <v>13.47368121147156</v>
+        <v>11.52916884422302</v>
       </c>
       <c r="I42" t="n">
-        <v>16.49749422073364</v>
+        <v>14.42243123054504</v>
       </c>
       <c r="J42" t="n">
-        <v>13.23032450675964</v>
+        <v>11.44240093231201</v>
       </c>
       <c r="K42" t="n">
-        <v>15.38126182556152</v>
+        <v>11.87424564361572</v>
       </c>
       <c r="L42" t="n">
-        <v>13.78307168483734</v>
+        <v>13.21306533813476</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>16.26254320144653</v>
+        <v>13.24932360649109</v>
       </c>
       <c r="C43" t="n">
-        <v>12.94383406639099</v>
+        <v>12.59830904006958</v>
       </c>
       <c r="D43" t="n">
-        <v>11.05785727500916</v>
+        <v>13.10994124412537</v>
       </c>
       <c r="E43" t="n">
-        <v>11.79295372962952</v>
+        <v>12.08568072319031</v>
       </c>
       <c r="F43" t="n">
-        <v>17.93678736686707</v>
+        <v>15.60626554489136</v>
       </c>
       <c r="G43" t="n">
-        <v>12.3679678440094</v>
+        <v>11.80742335319519</v>
       </c>
       <c r="H43" t="n">
-        <v>14.50557971000671</v>
+        <v>13.65249013900757</v>
       </c>
       <c r="I43" t="n">
-        <v>12.3271050453186</v>
+        <v>13.21865105628967</v>
       </c>
       <c r="J43" t="n">
-        <v>18.1113612651825</v>
+        <v>12.26919031143188</v>
       </c>
       <c r="K43" t="n">
-        <v>14.3290548324585</v>
+        <v>12.01487016677856</v>
       </c>
       <c r="L43" t="n">
-        <v>14.1635044336319</v>
+        <v>12.96121451854706</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>16.2416365146637</v>
+        <v>12.75489044189453</v>
       </c>
       <c r="C44" t="n">
-        <v>12.5485258102417</v>
+        <v>12.54245901107788</v>
       </c>
       <c r="D44" t="n">
-        <v>12.95749592781067</v>
+        <v>12.22730159759521</v>
       </c>
       <c r="E44" t="n">
-        <v>12.29119873046875</v>
+        <v>13.26652193069458</v>
       </c>
       <c r="F44" t="n">
-        <v>13.40683650970459</v>
+        <v>13.82203793525696</v>
       </c>
       <c r="G44" t="n">
-        <v>13.92303776741028</v>
+        <v>12.17145085334778</v>
       </c>
       <c r="H44" t="n">
-        <v>17.91232109069824</v>
+        <v>12.39585018157959</v>
       </c>
       <c r="I44" t="n">
-        <v>12.54254603385925</v>
+        <v>12.24824571609497</v>
       </c>
       <c r="J44" t="n">
-        <v>13.4522533416748</v>
+        <v>13.55674576759338</v>
       </c>
       <c r="K44" t="n">
-        <v>13.40236330032349</v>
+        <v>12.19837975502014</v>
       </c>
       <c r="L44" t="n">
-        <v>13.86782150268555</v>
+        <v>12.7183883190155</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>11.67779326438904</v>
+        <v>10.57871007919312</v>
       </c>
       <c r="C45" t="n">
-        <v>30.01414561271667</v>
+        <v>10.56075739860535</v>
       </c>
       <c r="D45" t="n">
-        <v>12.86425065994263</v>
+        <v>10.38522791862488</v>
       </c>
       <c r="E45" t="n">
-        <v>15.62221121788025</v>
+        <v>15.30307626724243</v>
       </c>
       <c r="F45" t="n">
-        <v>12.83927059173584</v>
+        <v>10.7482578754425</v>
       </c>
       <c r="G45" t="n">
-        <v>11.4992880821228</v>
+        <v>12.75788259506226</v>
       </c>
       <c r="H45" t="n">
-        <v>12.65776419639587</v>
+        <v>12.68102383613586</v>
       </c>
       <c r="I45" t="n">
-        <v>12.8193531036377</v>
+        <v>10.72432112693787</v>
       </c>
       <c r="J45" t="n">
-        <v>13.50134921073914</v>
+        <v>11.39652299880981</v>
       </c>
       <c r="K45" t="n">
-        <v>10.96545433998108</v>
+        <v>12.66114163398743</v>
       </c>
       <c r="L45" t="n">
-        <v>14.4460880279541</v>
+        <v>11.77969217300415</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>14.94460487365723</v>
+        <v>12.7708477973938</v>
       </c>
       <c r="C46" t="n">
-        <v>12.64855241775513</v>
+        <v>12.89950346946716</v>
       </c>
       <c r="D46" t="n">
-        <v>16.24780106544495</v>
+        <v>16.31038308143616</v>
       </c>
       <c r="E46" t="n">
-        <v>14.36068439483643</v>
+        <v>15.58133292198181</v>
       </c>
       <c r="F46" t="n">
-        <v>12.63478088378906</v>
+        <v>13.10994052886963</v>
       </c>
       <c r="G46" t="n">
-        <v>13.25919842720032</v>
+        <v>17.83530402183533</v>
       </c>
       <c r="H46" t="n">
-        <v>18.01923036575317</v>
+        <v>14.50620722770691</v>
       </c>
       <c r="I46" t="n">
-        <v>16.05109310150146</v>
+        <v>16.73125743865967</v>
       </c>
       <c r="J46" t="n">
-        <v>12.15550851821899</v>
+        <v>16.19967889785767</v>
       </c>
       <c r="K46" t="n">
-        <v>13.7394871711731</v>
+        <v>13.33733248710632</v>
       </c>
       <c r="L46" t="n">
-        <v>14.40609412193298</v>
+        <v>14.92817878723145</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>19.21533703804016</v>
+        <v>17.94201946258545</v>
       </c>
       <c r="C47" t="n">
-        <v>20.13021230697632</v>
+        <v>11.26886439323425</v>
       </c>
       <c r="D47" t="n">
-        <v>17.11886048316956</v>
+        <v>12.81373357772827</v>
       </c>
       <c r="E47" t="n">
-        <v>17.04456663131714</v>
+        <v>16.57367849349976</v>
       </c>
       <c r="F47" t="n">
-        <v>15.99876618385315</v>
+        <v>15.45167899131775</v>
       </c>
       <c r="G47" t="n">
-        <v>18.51828241348267</v>
+        <v>11.66680073738098</v>
       </c>
       <c r="H47" t="n">
-        <v>13.28662872314453</v>
+        <v>12.68807053565979</v>
       </c>
       <c r="I47" t="n">
-        <v>13.0288519859314</v>
+        <v>15.7897469997406</v>
       </c>
       <c r="J47" t="n">
-        <v>14.01628637313843</v>
+        <v>12.61925292015076</v>
       </c>
       <c r="K47" t="n">
-        <v>15.73087334632874</v>
+        <v>16.22261738777161</v>
       </c>
       <c r="L47" t="n">
-        <v>16.40886654853821</v>
+        <v>14.30364634990692</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>14.11556839942932</v>
+        <v>12.08667731285095</v>
       </c>
       <c r="C48" t="n">
-        <v>13.21166801452637</v>
+        <v>13.43706703186035</v>
       </c>
       <c r="D48" t="n">
-        <v>12.98720526695251</v>
+        <v>12.5993070602417</v>
       </c>
       <c r="E48" t="n">
-        <v>13.04903602600098</v>
+        <v>12.67709851264954</v>
       </c>
       <c r="F48" t="n">
-        <v>12.11305284500122</v>
+        <v>13.64251732826233</v>
       </c>
       <c r="G48" t="n">
-        <v>15.49763059616089</v>
+        <v>13.0151948928833</v>
       </c>
       <c r="H48" t="n">
-        <v>13.27399063110352</v>
+        <v>13.96964192390442</v>
       </c>
       <c r="I48" t="n">
-        <v>19.25588917732239</v>
+        <v>15.02980828285217</v>
       </c>
       <c r="J48" t="n">
-        <v>17.29257845878601</v>
+        <v>11.86327481269836</v>
       </c>
       <c r="K48" t="n">
-        <v>13.03310990333557</v>
+        <v>13.41113662719727</v>
       </c>
       <c r="L48" t="n">
-        <v>14.38297293186188</v>
+        <v>13.17317237854004</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>15.05782437324524</v>
+        <v>11.87424612045288</v>
       </c>
       <c r="C49" t="n">
-        <v>18.54613280296326</v>
+        <v>11.92213201522827</v>
       </c>
       <c r="D49" t="n">
-        <v>16.18599581718445</v>
+        <v>13.06207394599915</v>
       </c>
       <c r="E49" t="n">
-        <v>12.96849083900452</v>
+        <v>12.22730135917664</v>
       </c>
       <c r="F49" t="n">
-        <v>14.28267121315002</v>
+        <v>12.41579747200012</v>
       </c>
       <c r="G49" t="n">
-        <v>15.21520471572876</v>
+        <v>11.93907260894775</v>
       </c>
       <c r="H49" t="n">
-        <v>18.98770499229431</v>
+        <v>13.34431457519531</v>
       </c>
       <c r="I49" t="n">
-        <v>14.65487766265869</v>
+        <v>13.3123996257782</v>
       </c>
       <c r="J49" t="n">
-        <v>12.17678904533386</v>
+        <v>11.15417170524597</v>
       </c>
       <c r="K49" t="n">
-        <v>17.50304222106934</v>
+        <v>11.99392652511597</v>
       </c>
       <c r="L49" t="n">
-        <v>15.55787336826324</v>
+        <v>12.32454359531403</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>13.43203496932983</v>
+        <v>16.37665557861328</v>
       </c>
       <c r="C50" t="n">
-        <v>13.31287217140198</v>
+        <v>11.51919555664062</v>
       </c>
       <c r="D50" t="n">
-        <v>11.36877512931824</v>
+        <v>13.01519417762756</v>
       </c>
       <c r="E50" t="n">
-        <v>11.41694068908691</v>
+        <v>13.92897725105286</v>
       </c>
       <c r="F50" t="n">
-        <v>16.66358613967896</v>
+        <v>12.645183801651</v>
       </c>
       <c r="G50" t="n">
-        <v>11.67483520507812</v>
+        <v>11.28282690048218</v>
       </c>
       <c r="H50" t="n">
-        <v>13.00141382217407</v>
+        <v>11.39652442932129</v>
       </c>
       <c r="I50" t="n">
-        <v>13.24725890159607</v>
+        <v>11.70070958137512</v>
       </c>
       <c r="J50" t="n">
-        <v>12.69164156913757</v>
+        <v>14.20301818847656</v>
       </c>
       <c r="K50" t="n">
-        <v>13.52905559539795</v>
+        <v>12.16447019577026</v>
       </c>
       <c r="L50" t="n">
-        <v>13.03384141921997</v>
+        <v>12.82327556610107</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>11.93606853485107</v>
+        <v>11.97298145294189</v>
       </c>
       <c r="C51" t="n">
-        <v>10.83242917060852</v>
+        <v>13.05109930038452</v>
       </c>
       <c r="D51" t="n">
-        <v>11.02296209335327</v>
+        <v>16.5856466293335</v>
       </c>
       <c r="E51" t="n">
-        <v>11.11817860603333</v>
+        <v>12.113605260849</v>
       </c>
       <c r="F51" t="n">
-        <v>14.02032589912415</v>
+        <v>11.26886487007141</v>
       </c>
       <c r="G51" t="n">
-        <v>10.84393000602722</v>
+        <v>11.36061906814575</v>
       </c>
       <c r="H51" t="n">
-        <v>11.8826265335083</v>
+        <v>12.78281569480896</v>
       </c>
       <c r="I51" t="n">
-        <v>11.77686762809753</v>
+        <v>10.92777681350708</v>
       </c>
       <c r="J51" t="n">
-        <v>10.80390787124634</v>
+        <v>11.51919484138489</v>
       </c>
       <c r="K51" t="n">
-        <v>10.78491234779358</v>
+        <v>11.1940643787384</v>
       </c>
       <c r="L51" t="n">
-        <v>11.50222086906433</v>
+        <v>12.27766683101654</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>14.60052156925201</v>
+        <v>13.28608670711517</v>
       </c>
       <c r="C52" t="n">
-        <v>13.89497555732727</v>
+        <v>13.01380761146545</v>
       </c>
       <c r="D52" t="n">
-        <v>13.69333289146423</v>
+        <v>12.82951011180878</v>
       </c>
       <c r="E52" t="n">
-        <v>14.16027976989746</v>
+        <v>13.22643245697022</v>
       </c>
       <c r="F52" t="n">
-        <v>13.92141270637512</v>
+        <v>13.43026453018189</v>
       </c>
       <c r="G52" t="n">
-        <v>13.83006381034851</v>
+        <v>13.14127522468567</v>
       </c>
       <c r="H52" t="n">
-        <v>14.05534356117249</v>
+        <v>13.06487241744995</v>
       </c>
       <c r="I52" t="n">
-        <v>13.38311592102051</v>
+        <v>12.85781499385834</v>
       </c>
       <c r="J52" t="n">
-        <v>13.76451289176941</v>
+        <v>12.76778281211853</v>
       </c>
       <c r="K52" t="n">
-        <v>14.0107492351532</v>
+        <v>12.70600509166717</v>
       </c>
       <c r="L52" t="n">
-        <v>13.93143079137802</v>
+        <v>13.03238519573211</v>
       </c>
     </row>
   </sheetData>
